--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/29,06,26 Останкино КИ и ЗПФ/дв 29,06,26 Бердянск ост ки от Титенко.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/29,06,26 Останкино КИ и ЗПФ/дв 29,06,26 Бердянск ост ки от Титенко.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\06,26\29,06,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12EB7E53-EA7F-406A-B61E-F929BB20D2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDED0DA6-6E11-4BBA-A2FE-9DDC06976E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AC$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -993,7 +982,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX497"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="3" customWidth="1"/>
@@ -1004,17 +993,17 @@
     <col min="9" max="9" width="7" customWidth="1"/>
     <col min="10" max="10" width="1" customWidth="1"/>
     <col min="11" max="12" width="7" customWidth="1"/>
-    <col min="13" max="14" width="0.54296875" customWidth="1"/>
+    <col min="13" max="14" width="0.5703125" customWidth="1"/>
     <col min="15" max="19" width="7" customWidth="1"/>
     <col min="20" max="20" width="21" customWidth="1"/>
     <col min="21" max="22" width="5" customWidth="1"/>
     <col min="23" max="27" width="6" customWidth="1"/>
     <col min="28" max="28" width="32" style="22" customWidth="1"/>
-    <col min="29" max="29" width="7" customWidth="1"/>
-    <col min="30" max="50" width="3" customWidth="1"/>
+    <col min="29" max="30" width="7" customWidth="1"/>
+    <col min="31" max="50" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1066,7 +1055,7 @@
       <c r="AW1" s="1"/>
       <c r="AX1" s="1"/>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1118,7 +1107,7 @@
       <c r="AW2" s="1"/>
       <c r="AX2" s="1"/>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1228,7 +1217,7 @@
       <c r="AW3" s="1"/>
       <c r="AX3" s="1"/>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1296,7 +1285,7 @@
       <c r="AW4" s="1"/>
       <c r="AX4" s="1"/>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1377,7 +1366,10 @@
         <f>SUM(AC6:AC497)</f>
         <v>3768.532400000001</v>
       </c>
-      <c r="AD5" s="1"/>
+      <c r="AD5" s="4">
+        <f>SUM(AD6:AD497)</f>
+        <v>1058.3230000000001</v>
+      </c>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
       <c r="AG5" s="1"/>
@@ -1399,7 +1391,7 @@
       <c r="AW5" s="1"/>
       <c r="AX5" s="1"/>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
@@ -1479,7 +1471,10 @@
         <f t="shared" ref="AC6:AC35" si="5">G6*R6</f>
         <v>128.16</v>
       </c>
-      <c r="AD6" s="1"/>
+      <c r="AD6" s="1">
+        <f>Q6*G6</f>
+        <v>18.64</v>
+      </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
       <c r="AG6" s="1"/>
@@ -1501,7 +1496,7 @@
       <c r="AW6" s="1"/>
       <c r="AX6" s="1"/>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -1581,7 +1576,10 @@
         <f t="shared" si="5"/>
         <v>34.243400000000001</v>
       </c>
-      <c r="AD7" s="1"/>
+      <c r="AD7" s="1">
+        <f t="shared" ref="AD7:AD70" si="7">Q7*G7</f>
+        <v>4.5156000000000001</v>
+      </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
       <c r="AG7" s="1"/>
@@ -1603,7 +1601,7 @@
       <c r="AW7" s="1"/>
       <c r="AX7" s="1"/>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>37</v>
       </c>
@@ -1687,7 +1685,10 @@
         <f t="shared" si="5"/>
         <v>25.649999999999991</v>
       </c>
-      <c r="AD8" s="1"/>
+      <c r="AD8" s="1">
+        <f t="shared" si="7"/>
+        <v>6.35</v>
+      </c>
       <c r="AE8" s="1"/>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1"/>
@@ -1709,7 +1710,7 @@
       <c r="AW8" s="1"/>
       <c r="AX8" s="1"/>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
@@ -1793,7 +1794,10 @@
         <f t="shared" si="5"/>
         <v>269.17259999999999</v>
       </c>
-      <c r="AD9" s="1"/>
+      <c r="AD9" s="1">
+        <f t="shared" si="7"/>
+        <v>46.833399999999997</v>
+      </c>
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
       <c r="AG9" s="1"/>
@@ -1815,7 +1819,7 @@
       <c r="AW9" s="1"/>
       <c r="AX9" s="1"/>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>39</v>
       </c>
@@ -1897,7 +1901,10 @@
         <f t="shared" si="5"/>
         <v>18.398399999999999</v>
       </c>
-      <c r="AD10" s="1"/>
+      <c r="AD10" s="1">
+        <f t="shared" si="7"/>
+        <v>3.0775999999999999</v>
+      </c>
       <c r="AE10" s="1"/>
       <c r="AF10" s="1"/>
       <c r="AG10" s="1"/>
@@ -1919,7 +1926,7 @@
       <c r="AW10" s="1"/>
       <c r="AX10" s="1"/>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>40</v>
       </c>
@@ -1996,7 +2003,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AD11" s="1"/>
+      <c r="AD11" s="1">
+        <f t="shared" si="7"/>
+        <v>3.2698</v>
+      </c>
       <c r="AE11" s="1"/>
       <c r="AF11" s="1"/>
       <c r="AG11" s="1"/>
@@ -2018,7 +2028,7 @@
       <c r="AW11" s="1"/>
       <c r="AX11" s="1"/>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>41</v>
       </c>
@@ -2102,7 +2112,10 @@
         <f t="shared" si="5"/>
         <v>231.28760000000005</v>
       </c>
-      <c r="AD12" s="1"/>
+      <c r="AD12" s="1">
+        <f t="shared" si="7"/>
+        <v>49.622399999999999</v>
+      </c>
       <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
       <c r="AG12" s="1"/>
@@ -2124,7 +2137,7 @@
       <c r="AW12" s="1"/>
       <c r="AX12" s="1"/>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
@@ -2208,7 +2221,10 @@
         <f t="shared" si="5"/>
         <v>103.64999999999998</v>
       </c>
-      <c r="AD13" s="1"/>
+      <c r="AD13" s="1">
+        <f t="shared" si="7"/>
+        <v>10.95</v>
+      </c>
       <c r="AE13" s="1"/>
       <c r="AF13" s="1"/>
       <c r="AG13" s="1"/>
@@ -2230,7 +2246,7 @@
       <c r="AW13" s="1"/>
       <c r="AX13" s="1"/>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>43</v>
       </c>
@@ -2300,7 +2316,10 @@
       </c>
       <c r="AB14" s="19"/>
       <c r="AC14" s="10"/>
-      <c r="AD14" s="1"/>
+      <c r="AD14" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AE14" s="1"/>
       <c r="AF14" s="1"/>
       <c r="AG14" s="1"/>
@@ -2322,7 +2341,7 @@
       <c r="AW14" s="1"/>
       <c r="AX14" s="1"/>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>44</v>
       </c>
@@ -2401,7 +2420,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AD15" s="1"/>
+      <c r="AD15" s="1">
+        <f t="shared" si="7"/>
+        <v>11.567</v>
+      </c>
       <c r="AE15" s="1"/>
       <c r="AF15" s="1"/>
       <c r="AG15" s="1"/>
@@ -2423,7 +2445,7 @@
       <c r="AW15" s="1"/>
       <c r="AX15" s="1"/>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>45</v>
       </c>
@@ -2507,7 +2529,10 @@
         <f t="shared" si="5"/>
         <v>62.399999999999991</v>
       </c>
-      <c r="AD16" s="1"/>
+      <c r="AD16" s="1">
+        <f t="shared" si="7"/>
+        <v>7.6</v>
+      </c>
       <c r="AE16" s="1"/>
       <c r="AF16" s="1"/>
       <c r="AG16" s="1"/>
@@ -2529,7 +2554,7 @@
       <c r="AW16" s="1"/>
       <c r="AX16" s="1"/>
     </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
@@ -2613,7 +2638,10 @@
         <f t="shared" si="5"/>
         <v>48.08</v>
       </c>
-      <c r="AD17" s="1"/>
+      <c r="AD17" s="1">
+        <f t="shared" si="7"/>
+        <v>9.120000000000001</v>
+      </c>
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1"/>
@@ -2635,7 +2663,7 @@
       <c r="AW17" s="1"/>
       <c r="AX17" s="1"/>
     </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>47</v>
       </c>
@@ -2721,7 +2749,10 @@
         <f t="shared" si="5"/>
         <v>237.69860000000006</v>
       </c>
-      <c r="AD18" s="1"/>
+      <c r="AD18" s="1">
+        <f t="shared" si="7"/>
+        <v>43.4754</v>
+      </c>
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1"/>
@@ -2743,7 +2774,7 @@
       <c r="AW18" s="1"/>
       <c r="AX18" s="1"/>
     </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>49</v>
       </c>
@@ -2817,7 +2848,10 @@
       </c>
       <c r="AB19" s="19"/>
       <c r="AC19" s="10"/>
-      <c r="AD19" s="1"/>
+      <c r="AD19" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AE19" s="1"/>
       <c r="AF19" s="1"/>
       <c r="AG19" s="1"/>
@@ -2839,7 +2873,7 @@
       <c r="AW19" s="1"/>
       <c r="AX19" s="1"/>
     </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>50</v>
       </c>
@@ -2921,7 +2955,10 @@
         <f t="shared" si="5"/>
         <v>24.092800000000004</v>
       </c>
-      <c r="AD20" s="1"/>
+      <c r="AD20" s="1">
+        <f t="shared" si="7"/>
+        <v>3.0582000000000003</v>
+      </c>
       <c r="AE20" s="1"/>
       <c r="AF20" s="1"/>
       <c r="AG20" s="1"/>
@@ -2943,7 +2980,7 @@
       <c r="AW20" s="1"/>
       <c r="AX20" s="1"/>
     </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>51</v>
       </c>
@@ -3027,7 +3064,10 @@
         <f t="shared" si="5"/>
         <v>3.9200000000000048</v>
       </c>
-      <c r="AD21" s="1"/>
+      <c r="AD21" s="1">
+        <f t="shared" si="7"/>
+        <v>8.8800000000000008</v>
+      </c>
       <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
       <c r="AG21" s="1"/>
@@ -3049,7 +3089,7 @@
       <c r="AW21" s="1"/>
       <c r="AX21" s="1"/>
     </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>52</v>
       </c>
@@ -3133,7 +3173,10 @@
         <f t="shared" si="5"/>
         <v>84.753999999999991</v>
       </c>
-      <c r="AD22" s="1"/>
+      <c r="AD22" s="1">
+        <f t="shared" si="7"/>
+        <v>26.175999999999998</v>
+      </c>
       <c r="AE22" s="1"/>
       <c r="AF22" s="1"/>
       <c r="AG22" s="1"/>
@@ -3155,7 +3198,7 @@
       <c r="AW22" s="1"/>
       <c r="AX22" s="1"/>
     </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>53</v>
       </c>
@@ -3239,7 +3282,10 @@
         <f t="shared" si="5"/>
         <v>40.92</v>
       </c>
-      <c r="AD23" s="1"/>
+      <c r="AD23" s="1">
+        <f t="shared" si="7"/>
+        <v>8.58</v>
+      </c>
       <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
       <c r="AG23" s="1"/>
@@ -3261,7 +3307,7 @@
       <c r="AW23" s="1"/>
       <c r="AX23" s="1"/>
     </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>54</v>
       </c>
@@ -3338,7 +3384,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AD24" s="1"/>
+      <c r="AD24" s="1">
+        <f t="shared" si="7"/>
+        <v>2.25</v>
+      </c>
       <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
       <c r="AG24" s="1"/>
@@ -3360,7 +3409,7 @@
       <c r="AW24" s="1"/>
       <c r="AX24" s="1"/>
     </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>55</v>
       </c>
@@ -3440,7 +3489,10 @@
         <f t="shared" si="5"/>
         <v>1.8899999999999997</v>
       </c>
-      <c r="AD25" s="1"/>
+      <c r="AD25" s="1">
+        <f t="shared" si="7"/>
+        <v>0.21</v>
+      </c>
       <c r="AE25" s="1"/>
       <c r="AF25" s="1"/>
       <c r="AG25" s="1"/>
@@ -3462,7 +3514,7 @@
       <c r="AW25" s="1"/>
       <c r="AX25" s="1"/>
     </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -3546,7 +3598,10 @@
         <f t="shared" si="5"/>
         <v>27.418000000000006</v>
       </c>
-      <c r="AD26" s="1"/>
+      <c r="AD26" s="1">
+        <f t="shared" si="7"/>
+        <v>10.058</v>
+      </c>
       <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
       <c r="AG26" s="1"/>
@@ -3568,7 +3623,7 @@
       <c r="AW26" s="1"/>
       <c r="AX26" s="1"/>
     </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>57</v>
       </c>
@@ -3652,7 +3707,10 @@
         <f t="shared" si="5"/>
         <v>4.7160000000000029</v>
       </c>
-      <c r="AD27" s="1"/>
+      <c r="AD27" s="1">
+        <f t="shared" si="7"/>
+        <v>2.754</v>
+      </c>
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
       <c r="AG27" s="1"/>
@@ -3674,7 +3732,7 @@
       <c r="AW27" s="1"/>
       <c r="AX27" s="1"/>
     </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>58</v>
       </c>
@@ -3758,7 +3816,10 @@
         <f t="shared" si="5"/>
         <v>5.04</v>
       </c>
-      <c r="AD28" s="1"/>
+      <c r="AD28" s="1">
+        <f t="shared" si="7"/>
+        <v>1.98</v>
+      </c>
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
       <c r="AG28" s="1"/>
@@ -3780,7 +3841,7 @@
       <c r="AW28" s="1"/>
       <c r="AX28" s="1"/>
     </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>59</v>
       </c>
@@ -3852,7 +3913,10 @@
       </c>
       <c r="AB29" s="19"/>
       <c r="AC29" s="10"/>
-      <c r="AD29" s="1"/>
+      <c r="AD29" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
       <c r="AG29" s="1"/>
@@ -3874,7 +3938,7 @@
       <c r="AW29" s="1"/>
       <c r="AX29" s="1"/>
     </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>60</v>
       </c>
@@ -3953,7 +4017,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AD30" s="1"/>
+      <c r="AD30" s="1">
+        <f t="shared" si="7"/>
+        <v>1.47</v>
+      </c>
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
       <c r="AG30" s="1"/>
@@ -3975,7 +4042,7 @@
       <c r="AW30" s="1"/>
       <c r="AX30" s="1"/>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
@@ -4059,7 +4126,10 @@
         <f t="shared" si="5"/>
         <v>276.07099999999997</v>
       </c>
-      <c r="AD31" s="1"/>
+      <c r="AD31" s="1">
+        <f t="shared" si="7"/>
+        <v>62.065999999999995</v>
+      </c>
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
       <c r="AG31" s="1"/>
@@ -4081,7 +4151,7 @@
       <c r="AW31" s="1"/>
       <c r="AX31" s="1"/>
     </row>
-    <row r="32" spans="1:50" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:50" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>62</v>
       </c>
@@ -4159,7 +4229,10 @@
         <v>143</v>
       </c>
       <c r="AC32" s="10"/>
-      <c r="AD32" s="1"/>
+      <c r="AD32" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
       <c r="AG32" s="1"/>
@@ -4181,7 +4254,7 @@
       <c r="AW32" s="1"/>
       <c r="AX32" s="1"/>
     </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>63</v>
       </c>
@@ -4265,7 +4338,10 @@
         <f t="shared" si="5"/>
         <v>70.239999999999995</v>
       </c>
-      <c r="AD33" s="1"/>
+      <c r="AD33" s="1">
+        <f t="shared" si="7"/>
+        <v>8.9599999999999991</v>
+      </c>
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
       <c r="AG33" s="1"/>
@@ -4287,7 +4363,7 @@
       <c r="AW33" s="1"/>
       <c r="AX33" s="1"/>
     </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>64</v>
       </c>
@@ -4371,7 +4447,10 @@
         <f t="shared" si="5"/>
         <v>42.800000000000004</v>
       </c>
-      <c r="AD34" s="1"/>
+      <c r="AD34" s="1">
+        <f t="shared" si="7"/>
+        <v>32</v>
+      </c>
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
       <c r="AG34" s="1"/>
@@ -4393,7 +4472,7 @@
       <c r="AW34" s="1"/>
       <c r="AX34" s="1"/>
     </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>65</v>
       </c>
@@ -4479,7 +4558,10 @@
         <f t="shared" si="5"/>
         <v>201.20000000000002</v>
       </c>
-      <c r="AD35" s="1"/>
+      <c r="AD35" s="1">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
       <c r="AG35" s="1"/>
@@ -4501,7 +4583,7 @@
       <c r="AW35" s="1"/>
       <c r="AX35" s="1"/>
     </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>66</v>
       </c>
@@ -4571,7 +4653,10 @@
       </c>
       <c r="AB36" s="19"/>
       <c r="AC36" s="10"/>
-      <c r="AD36" s="1"/>
+      <c r="AD36" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AE36" s="1"/>
       <c r="AF36" s="1"/>
       <c r="AG36" s="1"/>
@@ -4593,7 +4678,7 @@
       <c r="AW36" s="1"/>
       <c r="AX36" s="1"/>
     </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>69</v>
       </c>
@@ -4676,10 +4761,13 @@
         <v>48</v>
       </c>
       <c r="AC37" s="1">
-        <f t="shared" ref="AC37:AC68" si="7">G37*R37</f>
+        <f t="shared" ref="AC37:AC68" si="8">G37*R37</f>
         <v>283.36000000000007</v>
       </c>
-      <c r="AD37" s="1"/>
+      <c r="AD37" s="1">
+        <f t="shared" si="7"/>
+        <v>34.880000000000003</v>
+      </c>
       <c r="AE37" s="1"/>
       <c r="AF37" s="1"/>
       <c r="AG37" s="1"/>
@@ -4701,7 +4789,7 @@
       <c r="AW37" s="1"/>
       <c r="AX37" s="1"/>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>70</v>
       </c>
@@ -4734,7 +4822,7 @@
         <v>307</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="8">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="9">E38-K38</f>
         <v>-62</v>
       </c>
       <c r="M38" s="1"/>
@@ -4746,11 +4834,11 @@
         <v>100</v>
       </c>
       <c r="Q38" s="1">
-        <f t="shared" ref="Q38:Q69" si="9">E38/5</f>
+        <f t="shared" ref="Q38:Q69" si="10">E38/5</f>
         <v>49</v>
       </c>
       <c r="R38" s="5">
-        <f t="shared" ref="R38:R90" si="10">14*Q38-P38-O38-F38</f>
+        <f t="shared" ref="R38:R90" si="11">14*Q38-P38-O38-F38</f>
         <v>404</v>
       </c>
       <c r="S38" s="5">
@@ -4758,11 +4846,11 @@
       </c>
       <c r="T38" s="1"/>
       <c r="U38" s="1">
-        <f t="shared" ref="U38:U69" si="11">(F38+O38+P38+R38)/Q38</f>
+        <f t="shared" ref="U38:U69" si="12">(F38+O38+P38+R38)/Q38</f>
         <v>14</v>
       </c>
       <c r="V38" s="1">
-        <f t="shared" ref="V38:V69" si="12">(F38+O38+P38)/Q38</f>
+        <f t="shared" ref="V38:V69" si="13">(F38+O38+P38)/Q38</f>
         <v>5.7551020408163263</v>
       </c>
       <c r="W38" s="1">
@@ -4784,10 +4872,13 @@
         <v>48</v>
       </c>
       <c r="AC38" s="1">
+        <f t="shared" si="8"/>
+        <v>40.400000000000006</v>
+      </c>
+      <c r="AD38" s="1">
         <f t="shared" si="7"/>
-        <v>40.400000000000006</v>
-      </c>
-      <c r="AD38" s="1"/>
+        <v>4.9000000000000004</v>
+      </c>
       <c r="AE38" s="1"/>
       <c r="AF38" s="1"/>
       <c r="AG38" s="1"/>
@@ -4809,7 +4900,7 @@
       <c r="AW38" s="1"/>
       <c r="AX38" s="1"/>
     </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>71</v>
       </c>
@@ -4842,7 +4933,7 @@
         <v>192</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-23</v>
       </c>
       <c r="M39" s="1"/>
@@ -4854,11 +4945,11 @@
         <v>100</v>
       </c>
       <c r="Q39" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>33.799999999999997</v>
       </c>
       <c r="R39" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>105.19999999999993</v>
       </c>
       <c r="S39" s="5">
@@ -4866,11 +4957,11 @@
       </c>
       <c r="T39" s="1"/>
       <c r="U39" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="V39" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10.887573964497042</v>
       </c>
       <c r="W39" s="1">
@@ -4890,10 +4981,13 @@
       </c>
       <c r="AB39" s="17"/>
       <c r="AC39" s="1">
+        <f t="shared" si="8"/>
+        <v>10.519999999999994</v>
+      </c>
+      <c r="AD39" s="1">
         <f t="shared" si="7"/>
-        <v>10.519999999999994</v>
-      </c>
-      <c r="AD39" s="1"/>
+        <v>3.38</v>
+      </c>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
       <c r="AG39" s="1"/>
@@ -4915,7 +5009,7 @@
       <c r="AW39" s="1"/>
       <c r="AX39" s="1"/>
     </row>
-    <row r="40" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>72</v>
       </c>
@@ -4948,7 +5042,7 @@
         <v>23</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-9</v>
       </c>
       <c r="M40" s="1"/>
@@ -4960,20 +5054,20 @@
         <v>0</v>
       </c>
       <c r="Q40" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.8</v>
       </c>
       <c r="R40" s="5"/>
       <c r="S40" s="5"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1">
-        <f t="shared" si="11"/>
-        <v>31.428571428571431</v>
-      </c>
-      <c r="V40" s="1">
         <f t="shared" si="12"/>
         <v>31.428571428571431</v>
       </c>
+      <c r="V40" s="1">
+        <f t="shared" si="13"/>
+        <v>31.428571428571431</v>
+      </c>
       <c r="W40" s="1">
         <v>-0.4</v>
       </c>
@@ -4991,10 +5085,13 @@
       </c>
       <c r="AB40" s="17"/>
       <c r="AC40" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD40" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD40" s="1"/>
+        <v>0.27999999999999997</v>
+      </c>
       <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
       <c r="AG40" s="1"/>
@@ -5016,7 +5113,7 @@
       <c r="AW40" s="1"/>
       <c r="AX40" s="1"/>
     </row>
-    <row r="41" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>73</v>
       </c>
@@ -5045,7 +5142,7 @@
         <v>6.7</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.46499999999999986</v>
       </c>
       <c r="M41" s="1"/>
@@ -5057,20 +5154,20 @@
         <v>45.5</v>
       </c>
       <c r="Q41" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.4330000000000001</v>
       </c>
       <c r="R41" s="5"/>
       <c r="S41" s="5"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1">
-        <f t="shared" si="11"/>
-        <v>72.759944173063502</v>
-      </c>
-      <c r="V41" s="1">
         <f t="shared" si="12"/>
         <v>72.759944173063502</v>
       </c>
+      <c r="V41" s="1">
+        <f t="shared" si="13"/>
+        <v>72.759944173063502</v>
+      </c>
       <c r="W41" s="1">
         <v>7.9530000000000003</v>
       </c>
@@ -5090,10 +5187,13 @@
         <v>144</v>
       </c>
       <c r="AC41" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD41" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD41" s="1"/>
+        <v>1.4330000000000001</v>
+      </c>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
       <c r="AG41" s="1"/>
@@ -5115,7 +5215,7 @@
       <c r="AW41" s="1"/>
       <c r="AX41" s="1"/>
     </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>74</v>
       </c>
@@ -5146,7 +5246,7 @@
         <v>120</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-52</v>
       </c>
       <c r="M42" s="1"/>
@@ -5158,20 +5258,20 @@
         <v>61.5</v>
       </c>
       <c r="Q42" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>13.6</v>
       </c>
       <c r="R42" s="5"/>
       <c r="S42" s="5"/>
       <c r="T42" s="1"/>
       <c r="U42" s="1">
-        <f t="shared" si="11"/>
-        <v>21.25</v>
-      </c>
-      <c r="V42" s="1">
         <f t="shared" si="12"/>
         <v>21.25</v>
       </c>
+      <c r="V42" s="1">
+        <f t="shared" si="13"/>
+        <v>21.25</v>
+      </c>
       <c r="W42" s="1">
         <v>27</v>
       </c>
@@ -5189,10 +5289,13 @@
       </c>
       <c r="AB42" s="17"/>
       <c r="AC42" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD42" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD42" s="1"/>
+        <v>5.44</v>
+      </c>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
       <c r="AG42" s="1"/>
@@ -5214,7 +5317,7 @@
       <c r="AW42" s="1"/>
       <c r="AX42" s="1"/>
     </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>75</v>
       </c>
@@ -5245,7 +5348,7 @@
         <v>39</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-32</v>
       </c>
       <c r="M43" s="1"/>
@@ -5257,20 +5360,20 @@
         <v>220</v>
       </c>
       <c r="Q43" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.4</v>
       </c>
       <c r="R43" s="5"/>
       <c r="S43" s="5"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1">
-        <f t="shared" si="11"/>
-        <v>344.28571428571433</v>
-      </c>
-      <c r="V43" s="1">
         <f t="shared" si="12"/>
         <v>344.28571428571433</v>
       </c>
+      <c r="V43" s="1">
+        <f t="shared" si="13"/>
+        <v>344.28571428571433</v>
+      </c>
       <c r="W43" s="1">
         <v>37.6</v>
       </c>
@@ -5288,10 +5391,13 @@
       </c>
       <c r="AB43" s="17"/>
       <c r="AC43" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD43" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD43" s="1"/>
+        <v>0.42</v>
+      </c>
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
       <c r="AG43" s="1"/>
@@ -5313,7 +5419,7 @@
       <c r="AW43" s="1"/>
       <c r="AX43" s="1"/>
     </row>
-    <row r="44" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>76</v>
       </c>
@@ -5346,7 +5452,7 @@
         <v>198.2</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-39.006999999999977</v>
       </c>
       <c r="M44" s="1"/>
@@ -5358,7 +5464,7 @@
         <v>28</v>
       </c>
       <c r="Q44" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>31.838600000000003</v>
       </c>
       <c r="R44" s="5">
@@ -5370,11 +5476,11 @@
       </c>
       <c r="T44" s="1"/>
       <c r="U44" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="V44" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.009818270903871</v>
       </c>
       <c r="W44" s="1">
@@ -5394,10 +5500,13 @@
       </c>
       <c r="AB44" s="17"/>
       <c r="AC44" s="1">
+        <f t="shared" si="8"/>
+        <v>254.39620000000005</v>
+      </c>
+      <c r="AD44" s="1">
         <f t="shared" si="7"/>
-        <v>254.39620000000005</v>
-      </c>
-      <c r="AD44" s="1"/>
+        <v>31.838600000000003</v>
+      </c>
       <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
       <c r="AG44" s="1"/>
@@ -5419,7 +5528,7 @@
       <c r="AW44" s="1"/>
       <c r="AX44" s="1"/>
     </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>77</v>
       </c>
@@ -5452,7 +5561,7 @@
         <v>69.3</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-3.847999999999999</v>
       </c>
       <c r="M45" s="1"/>
@@ -5464,11 +5573,11 @@
         <v>7</v>
       </c>
       <c r="Q45" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>13.090399999999999</v>
       </c>
       <c r="R45" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>91.421599999999984</v>
       </c>
       <c r="S45" s="5">
@@ -5476,11 +5585,11 @@
       </c>
       <c r="T45" s="1"/>
       <c r="U45" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="V45" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.0161339607651412</v>
       </c>
       <c r="W45" s="1">
@@ -5500,10 +5609,13 @@
       </c>
       <c r="AB45" s="17"/>
       <c r="AC45" s="1">
+        <f t="shared" si="8"/>
+        <v>91.421599999999984</v>
+      </c>
+      <c r="AD45" s="1">
         <f t="shared" si="7"/>
-        <v>91.421599999999984</v>
-      </c>
-      <c r="AD45" s="1"/>
+        <v>13.090399999999999</v>
+      </c>
       <c r="AE45" s="1"/>
       <c r="AF45" s="1"/>
       <c r="AG45" s="1"/>
@@ -5525,7 +5637,7 @@
       <c r="AW45" s="1"/>
       <c r="AX45" s="1"/>
     </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>78</v>
       </c>
@@ -5558,7 +5670,7 @@
         <v>37.1</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-12.129000000000001</v>
       </c>
       <c r="M46" s="1"/>
@@ -5570,20 +5682,20 @@
         <v>40</v>
       </c>
       <c r="Q46" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.9942000000000002</v>
       </c>
       <c r="R46" s="5"/>
       <c r="S46" s="5"/>
       <c r="T46" s="1"/>
       <c r="U46" s="1">
-        <f t="shared" si="11"/>
-        <v>36.69176244443554</v>
-      </c>
-      <c r="V46" s="1">
         <f t="shared" si="12"/>
         <v>36.69176244443554</v>
       </c>
+      <c r="V46" s="1">
+        <f t="shared" si="13"/>
+        <v>36.69176244443554</v>
+      </c>
       <c r="W46" s="1">
         <v>14.587400000000001</v>
       </c>
@@ -5601,10 +5713,13 @@
       </c>
       <c r="AB46" s="17"/>
       <c r="AC46" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD46" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD46" s="1"/>
+        <v>4.9942000000000002</v>
+      </c>
       <c r="AE46" s="1"/>
       <c r="AF46" s="1"/>
       <c r="AG46" s="1"/>
@@ -5626,7 +5741,7 @@
       <c r="AW46" s="1"/>
       <c r="AX46" s="1"/>
     </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>79</v>
       </c>
@@ -5655,7 +5770,7 @@
         <v>1</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
       <c r="M47" s="1"/>
@@ -5667,20 +5782,20 @@
         <v>0</v>
       </c>
       <c r="Q47" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="R47" s="5"/>
       <c r="S47" s="5"/>
       <c r="T47" s="1"/>
       <c r="U47" s="1" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V47" s="1" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V47" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W47" s="1">
         <v>-0.2</v>
       </c>
@@ -5700,10 +5815,13 @@
         <v>36</v>
       </c>
       <c r="AC47" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD47" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
       <c r="AF47" s="1"/>
       <c r="AG47" s="1"/>
@@ -5725,7 +5843,7 @@
       <c r="AW47" s="1"/>
       <c r="AX47" s="1"/>
     </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>80</v>
       </c>
@@ -5758,7 +5876,7 @@
         <v>51</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-10.579999999999998</v>
       </c>
       <c r="M48" s="1"/>
@@ -5770,20 +5888,20 @@
         <v>40</v>
       </c>
       <c r="Q48" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.0839999999999996</v>
       </c>
       <c r="R48" s="5"/>
       <c r="S48" s="5"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1">
-        <f t="shared" si="11"/>
-        <v>17.202127659574469</v>
-      </c>
-      <c r="V48" s="1">
         <f t="shared" si="12"/>
         <v>17.202127659574469</v>
       </c>
+      <c r="V48" s="1">
+        <f t="shared" si="13"/>
+        <v>17.202127659574469</v>
+      </c>
       <c r="W48" s="1">
         <v>12.8954</v>
       </c>
@@ -5803,10 +5921,13 @@
         <v>48</v>
       </c>
       <c r="AC48" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD48" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD48" s="1"/>
+        <v>8.0839999999999996</v>
+      </c>
       <c r="AE48" s="1"/>
       <c r="AF48" s="1"/>
       <c r="AG48" s="1"/>
@@ -5828,7 +5949,7 @@
       <c r="AW48" s="1"/>
       <c r="AX48" s="1"/>
     </row>
-    <row r="49" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>81</v>
       </c>
@@ -5861,7 +5982,7 @@
         <v>304</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-23</v>
       </c>
       <c r="M49" s="1"/>
@@ -5873,11 +5994,11 @@
         <v>150</v>
       </c>
       <c r="Q49" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>56.2</v>
       </c>
       <c r="R49" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>41.800000000000068</v>
       </c>
       <c r="S49" s="5">
@@ -5885,11 +6006,11 @@
       </c>
       <c r="T49" s="1"/>
       <c r="U49" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="V49" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13.256227758007118</v>
       </c>
       <c r="W49" s="1">
@@ -5909,10 +6030,13 @@
       </c>
       <c r="AB49" s="17"/>
       <c r="AC49" s="1">
+        <f t="shared" si="8"/>
+        <v>12.54000000000002</v>
+      </c>
+      <c r="AD49" s="1">
         <f t="shared" si="7"/>
-        <v>12.54000000000002</v>
-      </c>
-      <c r="AD49" s="1"/>
+        <v>16.86</v>
+      </c>
       <c r="AE49" s="1"/>
       <c r="AF49" s="1"/>
       <c r="AG49" s="1"/>
@@ -5934,7 +6058,7 @@
       <c r="AW49" s="1"/>
       <c r="AX49" s="1"/>
     </row>
-    <row r="50" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>82</v>
       </c>
@@ -5967,7 +6091,7 @@
         <v>15.1</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-2.738999999999999</v>
       </c>
       <c r="M50" s="1"/>
@@ -5979,20 +6103,20 @@
         <v>0</v>
       </c>
       <c r="Q50" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.4722</v>
       </c>
       <c r="R50" s="5"/>
       <c r="S50" s="5"/>
       <c r="T50" s="1"/>
       <c r="U50" s="1">
-        <f t="shared" si="11"/>
-        <v>36.130167462179436</v>
-      </c>
-      <c r="V50" s="1">
         <f t="shared" si="12"/>
         <v>36.130167462179436</v>
       </c>
+      <c r="V50" s="1">
+        <f t="shared" si="13"/>
+        <v>36.130167462179436</v>
+      </c>
       <c r="W50" s="1">
         <v>1.8528</v>
       </c>
@@ -6012,10 +6136,13 @@
         <v>144</v>
       </c>
       <c r="AC50" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD50" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD50" s="1"/>
+        <v>2.4722</v>
+      </c>
       <c r="AE50" s="1"/>
       <c r="AF50" s="1"/>
       <c r="AG50" s="1"/>
@@ -6037,7 +6164,7 @@
       <c r="AW50" s="1"/>
       <c r="AX50" s="1"/>
     </row>
-    <row r="51" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>83</v>
       </c>
@@ -6070,7 +6197,7 @@
         <v>599</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-67</v>
       </c>
       <c r="M51" s="1"/>
@@ -6082,7 +6209,7 @@
         <v>250</v>
       </c>
       <c r="Q51" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>106.4</v>
       </c>
       <c r="R51" s="5">
@@ -6094,11 +6221,11 @@
       </c>
       <c r="T51" s="1"/>
       <c r="U51" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
       <c r="V51" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>9.2387218045112771</v>
       </c>
       <c r="W51" s="1">
@@ -6120,10 +6247,13 @@
         <v>84</v>
       </c>
       <c r="AC51" s="1">
+        <f t="shared" si="8"/>
+        <v>140.07</v>
+      </c>
+      <c r="AD51" s="1">
         <f t="shared" si="7"/>
-        <v>140.07</v>
-      </c>
-      <c r="AD51" s="1"/>
+        <v>37.24</v>
+      </c>
       <c r="AE51" s="1"/>
       <c r="AF51" s="1"/>
       <c r="AG51" s="1"/>
@@ -6145,7 +6275,7 @@
       <c r="AW51" s="1"/>
       <c r="AX51" s="1"/>
     </row>
-    <row r="52" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>85</v>
       </c>
@@ -6178,7 +6308,7 @@
         <v>312</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-74</v>
       </c>
       <c r="M52" s="1"/>
@@ -6190,20 +6320,20 @@
         <v>400</v>
       </c>
       <c r="Q52" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>47.6</v>
       </c>
       <c r="R52" s="5"/>
       <c r="S52" s="5"/>
       <c r="T52" s="1"/>
       <c r="U52" s="1">
-        <f t="shared" si="11"/>
-        <v>17.352941176470587</v>
-      </c>
-      <c r="V52" s="1">
         <f t="shared" si="12"/>
         <v>17.352941176470587</v>
       </c>
+      <c r="V52" s="1">
+        <f t="shared" si="13"/>
+        <v>17.352941176470587</v>
+      </c>
       <c r="W52" s="1">
         <v>73.2</v>
       </c>
@@ -6221,10 +6351,13 @@
       </c>
       <c r="AB52" s="17"/>
       <c r="AC52" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD52" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD52" s="1"/>
+        <v>19.515999999999998</v>
+      </c>
       <c r="AE52" s="1"/>
       <c r="AF52" s="1"/>
       <c r="AG52" s="1"/>
@@ -6246,7 +6379,7 @@
       <c r="AW52" s="1"/>
       <c r="AX52" s="1"/>
     </row>
-    <row r="53" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>86</v>
       </c>
@@ -6279,7 +6412,7 @@
         <v>124</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-18</v>
       </c>
       <c r="M53" s="1"/>
@@ -6291,20 +6424,20 @@
         <v>0</v>
       </c>
       <c r="Q53" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21.2</v>
       </c>
       <c r="R53" s="5"/>
       <c r="S53" s="5"/>
       <c r="T53" s="1"/>
       <c r="U53" s="1">
-        <f t="shared" si="11"/>
-        <v>14.009433962264151</v>
-      </c>
-      <c r="V53" s="1">
         <f t="shared" si="12"/>
         <v>14.009433962264151</v>
       </c>
+      <c r="V53" s="1">
+        <f t="shared" si="13"/>
+        <v>14.009433962264151</v>
+      </c>
       <c r="W53" s="1">
         <v>22.8</v>
       </c>
@@ -6322,10 +6455,13 @@
       </c>
       <c r="AB53" s="17"/>
       <c r="AC53" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD53" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD53" s="1"/>
+        <v>8.6919999999999984</v>
+      </c>
       <c r="AE53" s="1"/>
       <c r="AF53" s="1"/>
       <c r="AG53" s="1"/>
@@ -6347,7 +6483,7 @@
       <c r="AW53" s="1"/>
       <c r="AX53" s="1"/>
     </row>
-    <row r="54" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>87</v>
       </c>
@@ -6374,7 +6510,7 @@
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M54" s="1"/>
@@ -6386,20 +6522,20 @@
         <v>0</v>
       </c>
       <c r="Q54" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="R54" s="5"/>
       <c r="S54" s="5"/>
       <c r="T54" s="1"/>
       <c r="U54" s="1" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V54" s="1" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V54" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W54" s="1">
         <v>0</v>
       </c>
@@ -6419,10 +6555,13 @@
         <v>36</v>
       </c>
       <c r="AC54" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD54" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD54" s="1"/>
       <c r="AE54" s="1"/>
       <c r="AF54" s="1"/>
       <c r="AG54" s="1"/>
@@ -6444,7 +6583,7 @@
       <c r="AW54" s="1"/>
       <c r="AX54" s="1"/>
     </row>
-    <row r="55" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>88</v>
       </c>
@@ -6475,7 +6614,7 @@
         <v>99</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-104</v>
       </c>
       <c r="M55" s="1"/>
@@ -6487,20 +6626,20 @@
         <v>0</v>
       </c>
       <c r="Q55" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-1</v>
       </c>
       <c r="R55" s="5"/>
       <c r="S55" s="5"/>
       <c r="T55" s="1"/>
       <c r="U55" s="1">
-        <f t="shared" si="11"/>
-        <v>-35</v>
-      </c>
-      <c r="V55" s="1">
         <f t="shared" si="12"/>
         <v>-35</v>
       </c>
+      <c r="V55" s="1">
+        <f t="shared" si="13"/>
+        <v>-35</v>
+      </c>
       <c r="W55" s="1">
         <v>-0.6</v>
       </c>
@@ -6520,10 +6659,13 @@
         <v>48</v>
       </c>
       <c r="AC55" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD55" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD55" s="1"/>
+        <v>-0.36</v>
+      </c>
       <c r="AE55" s="1"/>
       <c r="AF55" s="1"/>
       <c r="AG55" s="1"/>
@@ -6545,7 +6687,7 @@
       <c r="AW55" s="1"/>
       <c r="AX55" s="1"/>
     </row>
-    <row r="56" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>89</v>
       </c>
@@ -6572,7 +6714,7 @@
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M56" s="1"/>
@@ -6584,20 +6726,20 @@
         <v>0</v>
       </c>
       <c r="Q56" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="R56" s="5"/>
       <c r="S56" s="5"/>
       <c r="T56" s="1"/>
       <c r="U56" s="1" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V56" s="1" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V56" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W56" s="1">
         <v>0.21940000000000001</v>
       </c>
@@ -6615,10 +6757,13 @@
       </c>
       <c r="AB56" s="17"/>
       <c r="AC56" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD56" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD56" s="1"/>
       <c r="AE56" s="1"/>
       <c r="AF56" s="1"/>
       <c r="AG56" s="1"/>
@@ -6640,7 +6785,7 @@
       <c r="AW56" s="1"/>
       <c r="AX56" s="1"/>
     </row>
-    <row r="57" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>90</v>
       </c>
@@ -6673,7 +6818,7 @@
         <v>78</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-39</v>
       </c>
       <c r="M57" s="1"/>
@@ -6685,20 +6830,20 @@
         <v>0</v>
       </c>
       <c r="Q57" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.8</v>
       </c>
       <c r="R57" s="5"/>
       <c r="S57" s="5"/>
       <c r="T57" s="1"/>
       <c r="U57" s="1">
-        <f t="shared" si="11"/>
-        <v>17.692307692307693</v>
-      </c>
-      <c r="V57" s="1">
         <f t="shared" si="12"/>
         <v>17.692307692307693</v>
       </c>
+      <c r="V57" s="1">
+        <f t="shared" si="13"/>
+        <v>17.692307692307693</v>
+      </c>
       <c r="W57" s="1">
         <v>4.2</v>
       </c>
@@ -6716,10 +6861,13 @@
       </c>
       <c r="AB57" s="17"/>
       <c r="AC57" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD57" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD57" s="1"/>
+        <v>2.5739999999999998</v>
+      </c>
       <c r="AE57" s="1"/>
       <c r="AF57" s="1"/>
       <c r="AG57" s="1"/>
@@ -6741,7 +6889,7 @@
       <c r="AW57" s="1"/>
       <c r="AX57" s="1"/>
     </row>
-    <row r="58" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>91</v>
       </c>
@@ -6774,7 +6922,7 @@
         <v>141</v>
       </c>
       <c r="L58" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-60</v>
       </c>
       <c r="M58" s="10"/>
@@ -6786,20 +6934,20 @@
         <v>0</v>
       </c>
       <c r="Q58" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>16.2</v>
       </c>
       <c r="R58" s="12"/>
       <c r="S58" s="12"/>
       <c r="T58" s="10"/>
       <c r="U58" s="10">
-        <f t="shared" si="11"/>
-        <v>-5.0617283950617287</v>
-      </c>
-      <c r="V58" s="10">
         <f t="shared" si="12"/>
         <v>-5.0617283950617287</v>
       </c>
+      <c r="V58" s="10">
+        <f t="shared" si="13"/>
+        <v>-5.0617283950617287</v>
+      </c>
       <c r="W58" s="10">
         <v>2.8</v>
       </c>
@@ -6817,7 +6965,10 @@
       </c>
       <c r="AB58" s="19"/>
       <c r="AC58" s="10"/>
-      <c r="AD58" s="1"/>
+      <c r="AD58" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AE58" s="1"/>
       <c r="AF58" s="1"/>
       <c r="AG58" s="1"/>
@@ -6839,7 +6990,7 @@
       <c r="AW58" s="1"/>
       <c r="AX58" s="1"/>
     </row>
-    <row r="59" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>92</v>
       </c>
@@ -6870,7 +7021,7 @@
         <v>80</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-7</v>
       </c>
       <c r="M59" s="1"/>
@@ -6882,20 +7033,20 @@
         <v>0</v>
       </c>
       <c r="Q59" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>14.6</v>
       </c>
       <c r="R59" s="5"/>
       <c r="S59" s="5"/>
       <c r="T59" s="1"/>
       <c r="U59" s="1">
-        <f t="shared" si="11"/>
-        <v>32.19178082191781</v>
-      </c>
-      <c r="V59" s="1">
         <f t="shared" si="12"/>
         <v>32.19178082191781</v>
       </c>
+      <c r="V59" s="1">
+        <f t="shared" si="13"/>
+        <v>32.19178082191781</v>
+      </c>
       <c r="W59" s="1">
         <v>28</v>
       </c>
@@ -6915,10 +7066,13 @@
         <v>144</v>
       </c>
       <c r="AC59" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD59" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD59" s="1"/>
+        <v>5.84</v>
+      </c>
       <c r="AE59" s="1"/>
       <c r="AF59" s="1"/>
       <c r="AG59" s="1"/>
@@ -6940,7 +7094,7 @@
       <c r="AW59" s="1"/>
       <c r="AX59" s="1"/>
     </row>
-    <row r="60" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>93</v>
       </c>
@@ -6971,7 +7125,7 @@
         <v>20</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-7</v>
       </c>
       <c r="M60" s="1"/>
@@ -6983,20 +7137,20 @@
         <v>0</v>
       </c>
       <c r="Q60" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.6</v>
       </c>
       <c r="R60" s="5"/>
       <c r="S60" s="5"/>
       <c r="T60" s="1"/>
       <c r="U60" s="1">
-        <f t="shared" si="11"/>
-        <v>27.307692307692307</v>
-      </c>
-      <c r="V60" s="1">
         <f t="shared" si="12"/>
         <v>27.307692307692307</v>
       </c>
+      <c r="V60" s="1">
+        <f t="shared" si="13"/>
+        <v>27.307692307692307</v>
+      </c>
       <c r="W60" s="1">
         <v>2</v>
       </c>
@@ -7016,10 +7170,13 @@
         <v>36</v>
       </c>
       <c r="AC60" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD60" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD60" s="1"/>
+        <v>0.8580000000000001</v>
+      </c>
       <c r="AE60" s="1"/>
       <c r="AF60" s="1"/>
       <c r="AG60" s="1"/>
@@ -7041,7 +7198,7 @@
       <c r="AW60" s="1"/>
       <c r="AX60" s="1"/>
     </row>
-    <row r="61" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>94</v>
       </c>
@@ -7074,7 +7231,7 @@
         <v>190.4</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-10.711000000000013</v>
       </c>
       <c r="M61" s="1"/>
@@ -7086,11 +7243,11 @@
         <v>100</v>
       </c>
       <c r="Q61" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>35.937799999999996</v>
       </c>
       <c r="R61" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>136.60219999999998</v>
       </c>
       <c r="S61" s="5">
@@ -7098,11 +7255,11 @@
       </c>
       <c r="T61" s="1"/>
       <c r="U61" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="V61" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10.198927035043882</v>
       </c>
       <c r="W61" s="1">
@@ -7122,10 +7279,13 @@
       </c>
       <c r="AB61" s="17"/>
       <c r="AC61" s="1">
+        <f t="shared" si="8"/>
+        <v>136.60219999999998</v>
+      </c>
+      <c r="AD61" s="1">
         <f t="shared" si="7"/>
-        <v>136.60219999999998</v>
-      </c>
-      <c r="AD61" s="1"/>
+        <v>35.937799999999996</v>
+      </c>
       <c r="AE61" s="1"/>
       <c r="AF61" s="1"/>
       <c r="AG61" s="1"/>
@@ -7147,7 +7307,7 @@
       <c r="AW61" s="1"/>
       <c r="AX61" s="1"/>
     </row>
-    <row r="62" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>95</v>
       </c>
@@ -7178,7 +7338,7 @@
         <v>12</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-6</v>
       </c>
       <c r="M62" s="1"/>
@@ -7190,20 +7350,20 @@
         <v>50</v>
       </c>
       <c r="Q62" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.2</v>
       </c>
       <c r="R62" s="5"/>
       <c r="S62" s="5"/>
       <c r="T62" s="1"/>
       <c r="U62" s="1">
-        <f t="shared" si="11"/>
-        <v>108.33333333333334</v>
-      </c>
-      <c r="V62" s="1">
         <f t="shared" si="12"/>
         <v>108.33333333333334</v>
       </c>
+      <c r="V62" s="1">
+        <f t="shared" si="13"/>
+        <v>108.33333333333334</v>
+      </c>
       <c r="W62" s="1">
         <v>3.8</v>
       </c>
@@ -7223,10 +7383,13 @@
         <v>144</v>
       </c>
       <c r="AC62" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD62" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD62" s="1"/>
+        <v>0.12</v>
+      </c>
       <c r="AE62" s="1"/>
       <c r="AF62" s="1"/>
       <c r="AG62" s="1"/>
@@ -7248,7 +7411,7 @@
       <c r="AW62" s="1"/>
       <c r="AX62" s="1"/>
     </row>
-    <row r="63" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>96</v>
       </c>
@@ -7281,7 +7444,7 @@
         <v>95</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-43</v>
       </c>
       <c r="M63" s="1"/>
@@ -7293,20 +7456,20 @@
         <v>25</v>
       </c>
       <c r="Q63" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>10.4</v>
       </c>
       <c r="R63" s="5"/>
       <c r="S63" s="5"/>
       <c r="T63" s="1"/>
       <c r="U63" s="1">
-        <f t="shared" si="11"/>
-        <v>16.923076923076923</v>
-      </c>
-      <c r="V63" s="1">
         <f t="shared" si="12"/>
         <v>16.923076923076923</v>
       </c>
+      <c r="V63" s="1">
+        <f t="shared" si="13"/>
+        <v>16.923076923076923</v>
+      </c>
       <c r="W63" s="1">
         <v>15.8</v>
       </c>
@@ -7324,10 +7487,13 @@
       </c>
       <c r="AB63" s="17"/>
       <c r="AC63" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD63" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD63" s="1"/>
+        <v>4.16</v>
+      </c>
       <c r="AE63" s="1"/>
       <c r="AF63" s="1"/>
       <c r="AG63" s="1"/>
@@ -7349,7 +7515,7 @@
       <c r="AW63" s="1"/>
       <c r="AX63" s="1"/>
     </row>
-    <row r="64" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>97</v>
       </c>
@@ -7378,7 +7544,7 @@
         <v>12.5</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-3</v>
       </c>
       <c r="M64" s="1"/>
@@ -7390,20 +7556,20 @@
         <v>25</v>
       </c>
       <c r="Q64" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.9</v>
       </c>
       <c r="R64" s="5"/>
       <c r="S64" s="5"/>
       <c r="T64" s="1"/>
       <c r="U64" s="1">
-        <f t="shared" si="11"/>
-        <v>26.315789473684212</v>
-      </c>
-      <c r="V64" s="1">
         <f t="shared" si="12"/>
         <v>26.315789473684212</v>
       </c>
+      <c r="V64" s="1">
+        <f t="shared" si="13"/>
+        <v>26.315789473684212</v>
+      </c>
       <c r="W64" s="1">
         <v>1.615</v>
       </c>
@@ -7423,10 +7589,13 @@
         <v>98</v>
       </c>
       <c r="AC64" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD64" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD64" s="1"/>
+        <v>1.9</v>
+      </c>
       <c r="AE64" s="1"/>
       <c r="AF64" s="1"/>
       <c r="AG64" s="1"/>
@@ -7448,7 +7617,7 @@
       <c r="AW64" s="1"/>
       <c r="AX64" s="1"/>
     </row>
-    <row r="65" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>99</v>
       </c>
@@ -7479,7 +7648,7 @@
         <v>39</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
       <c r="M65" s="1"/>
@@ -7491,20 +7660,20 @@
         <v>0</v>
       </c>
       <c r="Q65" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.6</v>
       </c>
       <c r="R65" s="5"/>
       <c r="S65" s="5"/>
       <c r="T65" s="1"/>
       <c r="U65" s="1">
-        <f t="shared" si="11"/>
-        <v>25.789473684210527</v>
-      </c>
-      <c r="V65" s="1">
         <f t="shared" si="12"/>
         <v>25.789473684210527</v>
       </c>
+      <c r="V65" s="1">
+        <f t="shared" si="13"/>
+        <v>25.789473684210527</v>
+      </c>
       <c r="W65" s="1">
         <v>4.2</v>
       </c>
@@ -7524,10 +7693,13 @@
         <v>144</v>
       </c>
       <c r="AC65" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD65" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD65" s="1"/>
+        <v>4.5599999999999996</v>
+      </c>
       <c r="AE65" s="1"/>
       <c r="AF65" s="1"/>
       <c r="AG65" s="1"/>
@@ -7549,7 +7721,7 @@
       <c r="AW65" s="1"/>
       <c r="AX65" s="1"/>
     </row>
-    <row r="66" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
         <v>100</v>
       </c>
@@ -7576,7 +7748,7 @@
       </c>
       <c r="K66" s="10"/>
       <c r="L66" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M66" s="10"/>
@@ -7588,20 +7760,20 @@
         <v>32</v>
       </c>
       <c r="Q66" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="R66" s="12"/>
       <c r="S66" s="12"/>
       <c r="T66" s="10"/>
       <c r="U66" s="10" t="e">
-        <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V66" s="10" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V66" s="10" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W66" s="10">
         <v>0.311</v>
       </c>
@@ -7619,7 +7791,10 @@
       </c>
       <c r="AB66" s="19"/>
       <c r="AC66" s="10"/>
-      <c r="AD66" s="1"/>
+      <c r="AD66" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AE66" s="1"/>
       <c r="AF66" s="1"/>
       <c r="AG66" s="1"/>
@@ -7641,7 +7816,7 @@
       <c r="AW66" s="1"/>
       <c r="AX66" s="1"/>
     </row>
-    <row r="67" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>101</v>
       </c>
@@ -7674,7 +7849,7 @@
         <v>73</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-9</v>
       </c>
       <c r="M67" s="1"/>
@@ -7686,7 +7861,7 @@
         <v>0</v>
       </c>
       <c r="Q67" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12.8</v>
       </c>
       <c r="R67" s="5">
@@ -7698,11 +7873,11 @@
       </c>
       <c r="T67" s="1"/>
       <c r="U67" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
       <c r="V67" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.984375</v>
       </c>
       <c r="W67" s="1">
@@ -7722,10 +7897,13 @@
       </c>
       <c r="AB67" s="17"/>
       <c r="AC67" s="1">
+        <f t="shared" si="8"/>
+        <v>28.85</v>
+      </c>
+      <c r="AD67" s="1">
         <f t="shared" si="7"/>
-        <v>28.85</v>
-      </c>
-      <c r="AD67" s="1"/>
+        <v>3.2</v>
+      </c>
       <c r="AE67" s="1"/>
       <c r="AF67" s="1"/>
       <c r="AG67" s="1"/>
@@ -7747,7 +7925,7 @@
       <c r="AW67" s="1"/>
       <c r="AX67" s="1"/>
     </row>
-    <row r="68" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>102</v>
       </c>
@@ -7780,7 +7958,7 @@
         <v>15</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-4.6539999999999999</v>
       </c>
       <c r="M68" s="1"/>
@@ -7792,20 +7970,20 @@
         <v>0</v>
       </c>
       <c r="Q68" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.0691999999999999</v>
       </c>
       <c r="R68" s="5"/>
       <c r="S68" s="5"/>
       <c r="T68" s="1"/>
       <c r="U68" s="1">
-        <f t="shared" si="11"/>
-        <v>39.721148269862752</v>
-      </c>
-      <c r="V68" s="1">
         <f t="shared" si="12"/>
         <v>39.721148269862752</v>
       </c>
+      <c r="V68" s="1">
+        <f t="shared" si="13"/>
+        <v>39.721148269862752</v>
+      </c>
       <c r="W68" s="1">
         <v>0.59420000000000006</v>
       </c>
@@ -7823,10 +8001,13 @@
       </c>
       <c r="AB68" s="17"/>
       <c r="AC68" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD68" s="1">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AD68" s="1"/>
+        <v>2.0691999999999999</v>
+      </c>
       <c r="AE68" s="1"/>
       <c r="AF68" s="1"/>
       <c r="AG68" s="1"/>
@@ -7848,7 +8029,7 @@
       <c r="AW68" s="1"/>
       <c r="AX68" s="1"/>
     </row>
-    <row r="69" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>103</v>
       </c>
@@ -7879,7 +8060,7 @@
         <v>139</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-12</v>
       </c>
       <c r="M69" s="1"/>
@@ -7891,20 +8072,20 @@
         <v>150</v>
       </c>
       <c r="Q69" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>25.4</v>
       </c>
       <c r="R69" s="5"/>
       <c r="S69" s="5"/>
       <c r="T69" s="1"/>
       <c r="U69" s="1">
-        <f t="shared" si="11"/>
-        <v>18.818897637795278</v>
-      </c>
-      <c r="V69" s="1">
         <f t="shared" si="12"/>
         <v>18.818897637795278</v>
       </c>
+      <c r="V69" s="1">
+        <f t="shared" si="13"/>
+        <v>18.818897637795278</v>
+      </c>
       <c r="W69" s="1">
         <v>37.799999999999997</v>
       </c>
@@ -7922,10 +8103,13 @@
       </c>
       <c r="AB69" s="17"/>
       <c r="AC69" s="1">
-        <f t="shared" ref="AC69:AC90" si="13">G69*R69</f>
+        <f t="shared" ref="AC69:AC90" si="14">G69*R69</f>
         <v>0</v>
       </c>
-      <c r="AD69" s="1"/>
+      <c r="AD69" s="1">
+        <f t="shared" si="7"/>
+        <v>7.6199999999999992</v>
+      </c>
       <c r="AE69" s="1"/>
       <c r="AF69" s="1"/>
       <c r="AG69" s="1"/>
@@ -7947,7 +8131,7 @@
       <c r="AW69" s="1"/>
       <c r="AX69" s="1"/>
     </row>
-    <row r="70" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>104</v>
       </c>
@@ -7981,7 +8165,7 @@
         <v>802</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="14">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="15">E70-K70</f>
         <v>-48</v>
       </c>
       <c r="M70" s="1"/>
@@ -7993,11 +8177,11 @@
         <v>750</v>
       </c>
       <c r="Q70" s="1">
-        <f t="shared" ref="Q70:Q106" si="15">E70/5</f>
+        <f t="shared" ref="Q70:Q106" si="16">E70/5</f>
         <v>150.80000000000001</v>
       </c>
       <c r="R70" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>51.200000000000273</v>
       </c>
       <c r="S70" s="5">
@@ -8005,11 +8189,11 @@
       </c>
       <c r="T70" s="1"/>
       <c r="U70" s="1">
-        <f t="shared" ref="U70:U106" si="16">(F70+O70+P70+R70)/Q70</f>
+        <f t="shared" ref="U70:U106" si="17">(F70+O70+P70+R70)/Q70</f>
         <v>14</v>
       </c>
       <c r="V70" s="1">
-        <f t="shared" ref="V70:V106" si="17">(F70+O70+P70)/Q70</f>
+        <f t="shared" ref="V70:V106" si="18">(F70+O70+P70)/Q70</f>
         <v>13.660477453580901</v>
       </c>
       <c r="W70" s="1">
@@ -8029,10 +8213,13 @@
       </c>
       <c r="AB70" s="17"/>
       <c r="AC70" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>20.992000000000111</v>
       </c>
-      <c r="AD70" s="1"/>
+      <c r="AD70" s="1">
+        <f t="shared" si="7"/>
+        <v>61.828000000000003</v>
+      </c>
       <c r="AE70" s="1"/>
       <c r="AF70" s="1"/>
       <c r="AG70" s="1"/>
@@ -8054,7 +8241,7 @@
       <c r="AW70" s="1"/>
       <c r="AX70" s="1"/>
     </row>
-    <row r="71" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>105</v>
       </c>
@@ -8087,7 +8274,7 @@
         <v>97.6</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-15.631999999999991</v>
       </c>
       <c r="M71" s="1"/>
@@ -8099,20 +8286,20 @@
         <v>100</v>
       </c>
       <c r="Q71" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>16.393599999999999</v>
       </c>
       <c r="R71" s="5"/>
       <c r="S71" s="5"/>
       <c r="T71" s="1"/>
       <c r="U71" s="1">
-        <f t="shared" si="16"/>
-        <v>18.214547140347452</v>
-      </c>
-      <c r="V71" s="1">
         <f t="shared" si="17"/>
         <v>18.214547140347452</v>
       </c>
+      <c r="V71" s="1">
+        <f t="shared" si="18"/>
+        <v>18.214547140347452</v>
+      </c>
       <c r="W71" s="1">
         <v>23.993600000000001</v>
       </c>
@@ -8130,10 +8317,13 @@
       </c>
       <c r="AB71" s="17"/>
       <c r="AC71" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD71" s="1"/>
+      <c r="AD71" s="1">
+        <f t="shared" ref="AD71:AD106" si="19">Q71*G71</f>
+        <v>16.393599999999999</v>
+      </c>
       <c r="AE71" s="1"/>
       <c r="AF71" s="1"/>
       <c r="AG71" s="1"/>
@@ -8155,7 +8345,7 @@
       <c r="AW71" s="1"/>
       <c r="AX71" s="1"/>
     </row>
-    <row r="72" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>106</v>
       </c>
@@ -8188,7 +8378,7 @@
         <v>176</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-37</v>
       </c>
       <c r="M72" s="1"/>
@@ -8200,11 +8390,11 @@
         <v>180</v>
       </c>
       <c r="Q72" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>27.8</v>
       </c>
       <c r="R72" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>12.199999999999989</v>
       </c>
       <c r="S72" s="5">
@@ -8212,11 +8402,11 @@
       </c>
       <c r="T72" s="1"/>
       <c r="U72" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="V72" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>13.561151079136691</v>
       </c>
       <c r="W72" s="1">
@@ -8236,10 +8426,13 @@
       </c>
       <c r="AB72" s="17"/>
       <c r="AC72" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.269999999999996</v>
       </c>
-      <c r="AD72" s="1"/>
+      <c r="AD72" s="1">
+        <f t="shared" si="19"/>
+        <v>9.73</v>
+      </c>
       <c r="AE72" s="1"/>
       <c r="AF72" s="1"/>
       <c r="AG72" s="1"/>
@@ -8261,7 +8454,7 @@
       <c r="AW72" s="1"/>
       <c r="AX72" s="1"/>
     </row>
-    <row r="73" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>107</v>
       </c>
@@ -8294,7 +8487,7 @@
         <v>16.5</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.73300000000000054</v>
       </c>
       <c r="M73" s="1"/>
@@ -8306,21 +8499,21 @@
         <v>0</v>
       </c>
       <c r="Q73" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.1534</v>
       </c>
       <c r="R73" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>21.390599999999996</v>
       </c>
       <c r="S73" s="5"/>
       <c r="T73" s="1"/>
       <c r="U73" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="V73" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7.2166550390055182</v>
       </c>
       <c r="W73" s="1">
@@ -8340,10 +8533,13 @@
       </c>
       <c r="AB73" s="17"/>
       <c r="AC73" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>21.390599999999996</v>
       </c>
-      <c r="AD73" s="1"/>
+      <c r="AD73" s="1">
+        <f t="shared" si="19"/>
+        <v>3.1534</v>
+      </c>
       <c r="AE73" s="1"/>
       <c r="AF73" s="1"/>
       <c r="AG73" s="1"/>
@@ -8365,7 +8561,7 @@
       <c r="AW73" s="1"/>
       <c r="AX73" s="1"/>
     </row>
-    <row r="74" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>108</v>
       </c>
@@ -8398,7 +8594,7 @@
         <v>569</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-96</v>
       </c>
       <c r="M74" s="1"/>
@@ -8410,11 +8606,11 @@
         <v>250</v>
       </c>
       <c r="Q74" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>94.6</v>
       </c>
       <c r="R74" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>343.39999999999986</v>
       </c>
       <c r="S74" s="5">
@@ -8422,11 +8618,11 @@
       </c>
       <c r="T74" s="1"/>
       <c r="U74" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="V74" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>10.369978858350953</v>
       </c>
       <c r="W74" s="1">
@@ -8446,10 +8642,13 @@
       </c>
       <c r="AB74" s="17"/>
       <c r="AC74" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>140.79399999999993</v>
       </c>
-      <c r="AD74" s="1"/>
+      <c r="AD74" s="1">
+        <f t="shared" si="19"/>
+        <v>38.785999999999994</v>
+      </c>
       <c r="AE74" s="1"/>
       <c r="AF74" s="1"/>
       <c r="AG74" s="1"/>
@@ -8471,7 +8670,7 @@
       <c r="AW74" s="1"/>
       <c r="AX74" s="1"/>
     </row>
-    <row r="75" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
         <v>109</v>
       </c>
@@ -8502,7 +8701,7 @@
         <v>4.5</v>
       </c>
       <c r="L75" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-8.0449999999999999</v>
       </c>
       <c r="M75" s="10"/>
@@ -8514,20 +8713,20 @@
         <v>0</v>
       </c>
       <c r="Q75" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.70899999999999996</v>
       </c>
       <c r="R75" s="12"/>
       <c r="S75" s="12"/>
       <c r="T75" s="10"/>
       <c r="U75" s="10">
-        <f t="shared" si="16"/>
-        <v>2.2031029619181948</v>
-      </c>
-      <c r="V75" s="10">
         <f t="shared" si="17"/>
         <v>2.2031029619181948</v>
       </c>
+      <c r="V75" s="10">
+        <f t="shared" si="18"/>
+        <v>2.2031029619181948</v>
+      </c>
       <c r="W75" s="10">
         <v>-0.60739999999999994</v>
       </c>
@@ -8545,7 +8744,10 @@
       </c>
       <c r="AB75" s="19"/>
       <c r="AC75" s="10"/>
-      <c r="AD75" s="1"/>
+      <c r="AD75" s="1">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
       <c r="AE75" s="1"/>
       <c r="AF75" s="1"/>
       <c r="AG75" s="1"/>
@@ -8567,7 +8769,7 @@
       <c r="AW75" s="1"/>
       <c r="AX75" s="1"/>
     </row>
-    <row r="76" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>110</v>
       </c>
@@ -8598,7 +8800,7 @@
         <v>54.1</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-2.384999999999998</v>
       </c>
       <c r="M76" s="1"/>
@@ -8610,20 +8812,20 @@
         <v>75</v>
       </c>
       <c r="Q76" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>10.343</v>
       </c>
       <c r="R76" s="5"/>
       <c r="S76" s="5"/>
       <c r="T76" s="1"/>
       <c r="U76" s="1">
-        <f t="shared" si="16"/>
-        <v>19.033259209126946</v>
-      </c>
-      <c r="V76" s="1">
         <f t="shared" si="17"/>
         <v>19.033259209126946</v>
       </c>
+      <c r="V76" s="1">
+        <f t="shared" si="18"/>
+        <v>19.033259209126946</v>
+      </c>
       <c r="W76" s="1">
         <v>12.386799999999999</v>
       </c>
@@ -8641,10 +8843,13 @@
       </c>
       <c r="AB76" s="17"/>
       <c r="AC76" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD76" s="1"/>
+      <c r="AD76" s="1">
+        <f t="shared" si="19"/>
+        <v>10.343</v>
+      </c>
       <c r="AE76" s="1"/>
       <c r="AF76" s="1"/>
       <c r="AG76" s="1"/>
@@ -8666,7 +8871,7 @@
       <c r="AW76" s="1"/>
       <c r="AX76" s="1"/>
     </row>
-    <row r="77" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>111</v>
       </c>
@@ -8699,7 +8904,7 @@
         <v>149</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-24</v>
       </c>
       <c r="M77" s="1"/>
@@ -8711,11 +8916,11 @@
         <v>0</v>
       </c>
       <c r="Q77" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>25</v>
       </c>
       <c r="R77" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>182</v>
       </c>
       <c r="S77" s="5">
@@ -8723,11 +8928,11 @@
       </c>
       <c r="T77" s="1"/>
       <c r="U77" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="V77" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>6.72</v>
       </c>
       <c r="W77" s="1">
@@ -8747,10 +8952,13 @@
       </c>
       <c r="AB77" s="17"/>
       <c r="AC77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>54.6</v>
       </c>
-      <c r="AD77" s="1"/>
+      <c r="AD77" s="1">
+        <f t="shared" si="19"/>
+        <v>7.5</v>
+      </c>
       <c r="AE77" s="1"/>
       <c r="AF77" s="1"/>
       <c r="AG77" s="1"/>
@@ -8772,7 +8980,7 @@
       <c r="AW77" s="1"/>
       <c r="AX77" s="1"/>
     </row>
-    <row r="78" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>112</v>
       </c>
@@ -8805,7 +9013,7 @@
         <v>114</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-12</v>
       </c>
       <c r="M78" s="1"/>
@@ -8817,11 +9025,11 @@
         <v>0</v>
       </c>
       <c r="Q78" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>20.399999999999999</v>
       </c>
       <c r="R78" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>164.59999999999997</v>
       </c>
       <c r="S78" s="5">
@@ -8829,11 +9037,11 @@
       </c>
       <c r="T78" s="1"/>
       <c r="U78" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="V78" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.9313725490196081</v>
       </c>
       <c r="W78" s="1">
@@ -8853,10 +9061,13 @@
       </c>
       <c r="AB78" s="17"/>
       <c r="AC78" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>29.627999999999993</v>
       </c>
-      <c r="AD78" s="1"/>
+      <c r="AD78" s="1">
+        <f t="shared" si="19"/>
+        <v>3.6719999999999997</v>
+      </c>
       <c r="AE78" s="1"/>
       <c r="AF78" s="1"/>
       <c r="AG78" s="1"/>
@@ -8878,7 +9089,7 @@
       <c r="AW78" s="1"/>
       <c r="AX78" s="1"/>
     </row>
-    <row r="79" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>113</v>
       </c>
@@ -8911,7 +9122,7 @@
         <v>35.299999999999997</v>
       </c>
       <c r="L79" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-25.129999999999995</v>
       </c>
       <c r="M79" s="10"/>
@@ -8923,20 +9134,20 @@
         <v>0</v>
       </c>
       <c r="Q79" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.0339999999999998</v>
       </c>
       <c r="R79" s="12"/>
       <c r="S79" s="12"/>
       <c r="T79" s="10"/>
       <c r="U79" s="10">
-        <f t="shared" si="16"/>
-        <v>-5.5663716814159292</v>
-      </c>
-      <c r="V79" s="10">
         <f t="shared" si="17"/>
         <v>-5.5663716814159292</v>
       </c>
+      <c r="V79" s="10">
+        <f t="shared" si="18"/>
+        <v>-5.5663716814159292</v>
+      </c>
       <c r="W79" s="10">
         <v>0</v>
       </c>
@@ -8954,7 +9165,10 @@
       </c>
       <c r="AB79" s="19"/>
       <c r="AC79" s="10"/>
-      <c r="AD79" s="1"/>
+      <c r="AD79" s="1">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
       <c r="AE79" s="1"/>
       <c r="AF79" s="1"/>
       <c r="AG79" s="1"/>
@@ -8976,7 +9190,7 @@
       <c r="AW79" s="1"/>
       <c r="AX79" s="1"/>
     </row>
-    <row r="80" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>68</v>
       </c>
@@ -9010,7 +9224,7 @@
         <v>452</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-138</v>
       </c>
       <c r="M80" s="1"/>
@@ -9022,20 +9236,20 @@
         <v>200</v>
       </c>
       <c r="Q80" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>62.8</v>
       </c>
       <c r="R80" s="5"/>
       <c r="S80" s="5"/>
       <c r="T80" s="1"/>
       <c r="U80" s="1">
-        <f t="shared" si="16"/>
-        <v>16.146496815286625</v>
-      </c>
-      <c r="V80" s="1">
         <f t="shared" si="17"/>
         <v>16.146496815286625</v>
       </c>
+      <c r="V80" s="1">
+        <f t="shared" si="18"/>
+        <v>16.146496815286625</v>
+      </c>
       <c r="W80" s="1">
         <v>93.2</v>
       </c>
@@ -9053,10 +9267,13 @@
       </c>
       <c r="AB80" s="17"/>
       <c r="AC80" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD80" s="1"/>
+      <c r="AD80" s="1">
+        <f t="shared" si="19"/>
+        <v>21.979999999999997</v>
+      </c>
       <c r="AE80" s="1"/>
       <c r="AF80" s="1"/>
       <c r="AG80" s="1"/>
@@ -9078,7 +9295,7 @@
       <c r="AW80" s="1"/>
       <c r="AX80" s="1"/>
     </row>
-    <row r="81" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>114</v>
       </c>
@@ -9111,7 +9328,7 @@
         <v>119.5</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-15.691000000000003</v>
       </c>
       <c r="M81" s="1"/>
@@ -9123,20 +9340,20 @@
         <v>75</v>
       </c>
       <c r="Q81" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>20.761800000000001</v>
       </c>
       <c r="R81" s="5"/>
       <c r="S81" s="5"/>
       <c r="T81" s="1"/>
       <c r="U81" s="1">
-        <f t="shared" si="16"/>
-        <v>15.839763411650241</v>
-      </c>
-      <c r="V81" s="1">
         <f t="shared" si="17"/>
         <v>15.839763411650241</v>
       </c>
+      <c r="V81" s="1">
+        <f t="shared" si="18"/>
+        <v>15.839763411650241</v>
+      </c>
       <c r="W81" s="1">
         <v>27.382000000000001</v>
       </c>
@@ -9154,10 +9371,13 @@
       </c>
       <c r="AB81" s="17"/>
       <c r="AC81" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD81" s="1"/>
+      <c r="AD81" s="1">
+        <f t="shared" si="19"/>
+        <v>20.761800000000001</v>
+      </c>
       <c r="AE81" s="1"/>
       <c r="AF81" s="1"/>
       <c r="AG81" s="1"/>
@@ -9179,7 +9399,7 @@
       <c r="AW81" s="1"/>
       <c r="AX81" s="1"/>
     </row>
-    <row r="82" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>115</v>
       </c>
@@ -9212,7 +9432,7 @@
         <v>191.3</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-21.422000000000025</v>
       </c>
       <c r="M82" s="1"/>
@@ -9224,11 +9444,11 @@
         <v>200</v>
       </c>
       <c r="Q82" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>33.9756</v>
       </c>
       <c r="R82" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>130.64140000000003</v>
       </c>
       <c r="S82" s="5">
@@ -9236,11 +9456,11 @@
       </c>
       <c r="T82" s="1"/>
       <c r="U82" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="V82" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>10.154846419194952</v>
       </c>
       <c r="W82" s="1">
@@ -9260,10 +9480,13 @@
       </c>
       <c r="AB82" s="17"/>
       <c r="AC82" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>130.64140000000003</v>
       </c>
-      <c r="AD82" s="1"/>
+      <c r="AD82" s="1">
+        <f t="shared" si="19"/>
+        <v>33.9756</v>
+      </c>
       <c r="AE82" s="1"/>
       <c r="AF82" s="1"/>
       <c r="AG82" s="1"/>
@@ -9285,7 +9508,7 @@
       <c r="AW82" s="1"/>
       <c r="AX82" s="1"/>
     </row>
-    <row r="83" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>116</v>
       </c>
@@ -9318,7 +9541,7 @@
         <v>487</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-37</v>
       </c>
       <c r="M83" s="1"/>
@@ -9330,11 +9553,11 @@
         <v>315</v>
       </c>
       <c r="Q83" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>90</v>
       </c>
       <c r="R83" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>219</v>
       </c>
       <c r="S83" s="5">
@@ -9342,11 +9565,11 @@
       </c>
       <c r="T83" s="1"/>
       <c r="U83" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="V83" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>11.566666666666666</v>
       </c>
       <c r="W83" s="1">
@@ -9366,10 +9589,13 @@
       </c>
       <c r="AB83" s="17"/>
       <c r="AC83" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>76.649999999999991</v>
       </c>
-      <c r="AD83" s="1"/>
+      <c r="AD83" s="1">
+        <f t="shared" si="19"/>
+        <v>31.499999999999996</v>
+      </c>
       <c r="AE83" s="1"/>
       <c r="AF83" s="1"/>
       <c r="AG83" s="1"/>
@@ -9391,7 +9617,7 @@
       <c r="AW83" s="1"/>
       <c r="AX83" s="1"/>
     </row>
-    <row r="84" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>117</v>
       </c>
@@ -9424,7 +9650,7 @@
         <v>127</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-19</v>
       </c>
       <c r="M84" s="1"/>
@@ -9436,11 +9662,11 @@
         <v>60</v>
       </c>
       <c r="Q84" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>21.6</v>
       </c>
       <c r="R84" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>96.400000000000034</v>
       </c>
       <c r="S84" s="5">
@@ -9448,11 +9674,11 @@
       </c>
       <c r="T84" s="1"/>
       <c r="U84" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="V84" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>9.5370370370370363</v>
       </c>
       <c r="W84" s="1">
@@ -9472,10 +9698,13 @@
       </c>
       <c r="AB84" s="17"/>
       <c r="AC84" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>28.920000000000009</v>
       </c>
-      <c r="AD84" s="1"/>
+      <c r="AD84" s="1">
+        <f t="shared" si="19"/>
+        <v>6.48</v>
+      </c>
       <c r="AE84" s="1"/>
       <c r="AF84" s="1"/>
       <c r="AG84" s="1"/>
@@ -9497,7 +9726,7 @@
       <c r="AW84" s="1"/>
       <c r="AX84" s="1"/>
     </row>
-    <row r="85" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>118</v>
       </c>
@@ -9530,7 +9759,7 @@
         <v>45</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-13</v>
       </c>
       <c r="M85" s="1"/>
@@ -9542,20 +9771,20 @@
         <v>0</v>
       </c>
       <c r="Q85" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.4</v>
       </c>
       <c r="R85" s="5"/>
       <c r="S85" s="5"/>
       <c r="T85" s="1"/>
       <c r="U85" s="1">
-        <f t="shared" si="16"/>
-        <v>33.125</v>
-      </c>
-      <c r="V85" s="1">
         <f t="shared" si="17"/>
         <v>33.125</v>
       </c>
+      <c r="V85" s="1">
+        <f t="shared" si="18"/>
+        <v>33.125</v>
+      </c>
       <c r="W85" s="1">
         <v>3.4</v>
       </c>
@@ -9575,10 +9804,13 @@
         <v>36</v>
       </c>
       <c r="AC85" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD85" s="1"/>
+      <c r="AD85" s="1">
+        <f t="shared" si="19"/>
+        <v>1.92</v>
+      </c>
       <c r="AE85" s="1"/>
       <c r="AF85" s="1"/>
       <c r="AG85" s="1"/>
@@ -9600,7 +9832,7 @@
       <c r="AW85" s="1"/>
       <c r="AX85" s="1"/>
     </row>
-    <row r="86" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>119</v>
       </c>
@@ -9633,7 +9865,7 @@
         <v>301</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-27</v>
       </c>
       <c r="M86" s="1"/>
@@ -9645,11 +9877,11 @@
         <v>145</v>
       </c>
       <c r="Q86" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>54.8</v>
       </c>
       <c r="R86" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>212.69999999999993</v>
       </c>
       <c r="S86" s="5">
@@ -9657,11 +9889,11 @@
       </c>
       <c r="T86" s="1"/>
       <c r="U86" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="V86" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>10.118613138686133</v>
       </c>
       <c r="W86" s="1">
@@ -9681,10 +9913,13 @@
       </c>
       <c r="AB86" s="17"/>
       <c r="AC86" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>59.555999999999983</v>
       </c>
-      <c r="AD86" s="1"/>
+      <c r="AD86" s="1">
+        <f t="shared" si="19"/>
+        <v>15.344000000000001</v>
+      </c>
       <c r="AE86" s="1"/>
       <c r="AF86" s="1"/>
       <c r="AG86" s="1"/>
@@ -9706,7 +9941,7 @@
       <c r="AW86" s="1"/>
       <c r="AX86" s="1"/>
     </row>
-    <row r="87" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>120</v>
       </c>
@@ -9739,7 +9974,7 @@
         <v>319</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-97</v>
       </c>
       <c r="M87" s="1"/>
@@ -9751,20 +9986,20 @@
         <v>140</v>
       </c>
       <c r="Q87" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>44.4</v>
       </c>
       <c r="R87" s="5"/>
       <c r="S87" s="5"/>
       <c r="T87" s="1"/>
       <c r="U87" s="1">
-        <f t="shared" si="16"/>
-        <v>15.225225225225225</v>
-      </c>
-      <c r="V87" s="1">
         <f t="shared" si="17"/>
         <v>15.225225225225225</v>
       </c>
+      <c r="V87" s="1">
+        <f t="shared" si="18"/>
+        <v>15.225225225225225</v>
+      </c>
       <c r="W87" s="1">
         <v>60.6</v>
       </c>
@@ -9782,10 +10017,13 @@
       </c>
       <c r="AB87" s="17"/>
       <c r="AC87" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD87" s="1"/>
+      <c r="AD87" s="1">
+        <f t="shared" si="19"/>
+        <v>12.432</v>
+      </c>
       <c r="AE87" s="1"/>
       <c r="AF87" s="1"/>
       <c r="AG87" s="1"/>
@@ -9807,7 +10045,7 @@
       <c r="AW87" s="1"/>
       <c r="AX87" s="1"/>
     </row>
-    <row r="88" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>121</v>
       </c>
@@ -9840,7 +10078,7 @@
         <v>72</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-36</v>
       </c>
       <c r="M88" s="1"/>
@@ -9852,20 +10090,20 @@
         <v>0</v>
       </c>
       <c r="Q88" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>7.2</v>
       </c>
       <c r="R88" s="5"/>
       <c r="S88" s="5"/>
       <c r="T88" s="1"/>
       <c r="U88" s="1">
-        <f t="shared" si="16"/>
-        <v>27.5</v>
-      </c>
-      <c r="V88" s="1">
         <f t="shared" si="17"/>
         <v>27.5</v>
       </c>
+      <c r="V88" s="1">
+        <f t="shared" si="18"/>
+        <v>27.5</v>
+      </c>
       <c r="W88" s="1">
         <v>9.4</v>
       </c>
@@ -9883,10 +10121,13 @@
       </c>
       <c r="AB88" s="17"/>
       <c r="AC88" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AD88" s="1"/>
+      <c r="AD88" s="1">
+        <f t="shared" si="19"/>
+        <v>2.0160000000000005</v>
+      </c>
       <c r="AE88" s="1"/>
       <c r="AF88" s="1"/>
       <c r="AG88" s="1"/>
@@ -9908,7 +10149,7 @@
       <c r="AW88" s="1"/>
       <c r="AX88" s="1"/>
     </row>
-    <row r="89" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>122</v>
       </c>
@@ -9941,7 +10182,7 @@
         <v>284</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-68</v>
       </c>
       <c r="M89" s="1"/>
@@ -9953,11 +10194,11 @@
         <v>75</v>
       </c>
       <c r="Q89" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>43.2</v>
       </c>
       <c r="R89" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>209.80000000000007</v>
       </c>
       <c r="S89" s="5">
@@ -9965,11 +10206,11 @@
       </c>
       <c r="T89" s="1"/>
       <c r="U89" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="V89" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>9.1435185185185173</v>
       </c>
       <c r="W89" s="1">
@@ -9989,10 +10230,13 @@
       </c>
       <c r="AB89" s="17"/>
       <c r="AC89" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>58.744000000000028</v>
       </c>
-      <c r="AD89" s="1"/>
+      <c r="AD89" s="1">
+        <f t="shared" si="19"/>
+        <v>12.096000000000002</v>
+      </c>
       <c r="AE89" s="1"/>
       <c r="AF89" s="1"/>
       <c r="AG89" s="1"/>
@@ -10014,7 +10258,7 @@
       <c r="AW89" s="1"/>
       <c r="AX89" s="1"/>
     </row>
-    <row r="90" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>123</v>
       </c>
@@ -10047,7 +10291,7 @@
         <v>501</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-29</v>
       </c>
       <c r="M90" s="1"/>
@@ -10059,11 +10303,11 @@
         <v>325</v>
       </c>
       <c r="Q90" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>94.4</v>
       </c>
       <c r="R90" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>285.60000000000014</v>
       </c>
       <c r="S90" s="5">
@@ -10071,11 +10315,11 @@
       </c>
       <c r="T90" s="1"/>
       <c r="U90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="V90" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>10.974576271186439</v>
       </c>
       <c r="W90" s="1">
@@ -10095,10 +10339,13 @@
       </c>
       <c r="AB90" s="17"/>
       <c r="AC90" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>114.24000000000007</v>
       </c>
-      <c r="AD90" s="1"/>
+      <c r="AD90" s="1">
+        <f t="shared" si="19"/>
+        <v>37.760000000000005</v>
+      </c>
       <c r="AE90" s="1"/>
       <c r="AF90" s="1"/>
       <c r="AG90" s="1"/>
@@ -10120,7 +10367,7 @@
       <c r="AW90" s="1"/>
       <c r="AX90" s="1"/>
     </row>
-    <row r="91" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
         <v>124</v>
       </c>
@@ -10147,7 +10394,7 @@
         <v>8</v>
       </c>
       <c r="L91" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-8</v>
       </c>
       <c r="M91" s="10"/>
@@ -10155,20 +10402,20 @@
       <c r="O91" s="10"/>
       <c r="P91" s="10"/>
       <c r="Q91" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="R91" s="12"/>
       <c r="S91" s="12"/>
       <c r="T91" s="10"/>
       <c r="U91" s="10" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V91" s="10" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V91" s="10" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W91" s="10">
         <v>0</v>
       </c>
@@ -10186,7 +10433,10 @@
       </c>
       <c r="AB91" s="19"/>
       <c r="AC91" s="10"/>
-      <c r="AD91" s="1"/>
+      <c r="AD91" s="1">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
       <c r="AE91" s="1"/>
       <c r="AF91" s="1"/>
       <c r="AG91" s="1"/>
@@ -10208,7 +10458,7 @@
       <c r="AW91" s="1"/>
       <c r="AX91" s="1"/>
     </row>
-    <row r="92" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>126</v>
       </c>
@@ -10241,7 +10491,7 @@
         <v>16</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-3</v>
       </c>
       <c r="M92" s="1"/>
@@ -10253,20 +10503,20 @@
         <v>27</v>
       </c>
       <c r="Q92" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.6</v>
       </c>
       <c r="R92" s="5"/>
       <c r="S92" s="5"/>
       <c r="T92" s="1"/>
       <c r="U92" s="1">
-        <f t="shared" si="16"/>
-        <v>34.230769230769226</v>
-      </c>
-      <c r="V92" s="1">
         <f t="shared" si="17"/>
         <v>34.230769230769226</v>
       </c>
+      <c r="V92" s="1">
+        <f t="shared" si="18"/>
+        <v>34.230769230769226</v>
+      </c>
       <c r="W92" s="1">
         <v>8</v>
       </c>
@@ -10284,10 +10534,13 @@
       </c>
       <c r="AB92" s="17"/>
       <c r="AC92" s="1">
-        <f t="shared" ref="AC92:AC97" si="18">G92*R92</f>
+        <f t="shared" ref="AC92:AC97" si="20">G92*R92</f>
         <v>0</v>
       </c>
-      <c r="AD92" s="1"/>
+      <c r="AD92" s="1">
+        <f t="shared" si="19"/>
+        <v>0.26</v>
+      </c>
       <c r="AE92" s="1"/>
       <c r="AF92" s="1"/>
       <c r="AG92" s="1"/>
@@ -10309,7 +10562,7 @@
       <c r="AW92" s="1"/>
       <c r="AX92" s="1"/>
     </row>
-    <row r="93" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>127</v>
       </c>
@@ -10342,7 +10595,7 @@
         <v>41</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-9</v>
       </c>
       <c r="M93" s="1"/>
@@ -10354,11 +10607,11 @@
         <v>10.5</v>
       </c>
       <c r="Q93" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.4</v>
       </c>
       <c r="R93" s="5">
-        <f t="shared" ref="R93" si="19">14*Q93-P93-O93-F93</f>
+        <f t="shared" ref="R93" si="21">14*Q93-P93-O93-F93</f>
         <v>54.600000000000009</v>
       </c>
       <c r="S93" s="5">
@@ -10366,11 +10619,11 @@
       </c>
       <c r="T93" s="1"/>
       <c r="U93" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="V93" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.46875</v>
       </c>
       <c r="W93" s="1">
@@ -10390,10 +10643,13 @@
       </c>
       <c r="AB93" s="17"/>
       <c r="AC93" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>15.288000000000004</v>
       </c>
-      <c r="AD93" s="1"/>
+      <c r="AD93" s="1">
+        <f t="shared" si="19"/>
+        <v>1.7920000000000003</v>
+      </c>
       <c r="AE93" s="1"/>
       <c r="AF93" s="1"/>
       <c r="AG93" s="1"/>
@@ -10415,7 +10671,7 @@
       <c r="AW93" s="1"/>
       <c r="AX93" s="1"/>
     </row>
-    <row r="94" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>128</v>
       </c>
@@ -10446,7 +10702,7 @@
         <v>3</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M94" s="1"/>
@@ -10458,20 +10714,20 @@
         <v>0</v>
       </c>
       <c r="Q94" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.6</v>
       </c>
       <c r="R94" s="5"/>
       <c r="S94" s="5"/>
       <c r="T94" s="1"/>
       <c r="U94" s="1">
-        <f t="shared" si="16"/>
-        <v>11.666666666666668</v>
-      </c>
-      <c r="V94" s="1">
         <f t="shared" si="17"/>
         <v>11.666666666666668</v>
       </c>
+      <c r="V94" s="1">
+        <f t="shared" si="18"/>
+        <v>11.666666666666668</v>
+      </c>
       <c r="W94" s="1">
         <v>0.2</v>
       </c>
@@ -10489,10 +10745,13 @@
       </c>
       <c r="AB94" s="17"/>
       <c r="AC94" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AD94" s="1"/>
+      <c r="AD94" s="1">
+        <f t="shared" si="19"/>
+        <v>0.16800000000000001</v>
+      </c>
       <c r="AE94" s="1"/>
       <c r="AF94" s="1"/>
       <c r="AG94" s="1"/>
@@ -10514,7 +10773,7 @@
       <c r="AW94" s="1"/>
       <c r="AX94" s="1"/>
     </row>
-    <row r="95" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>129</v>
       </c>
@@ -10545,7 +10804,7 @@
         <v>82</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M95" s="1"/>
@@ -10557,20 +10816,20 @@
         <v>145</v>
       </c>
       <c r="Q95" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>16.399999999999999</v>
       </c>
       <c r="R95" s="5"/>
       <c r="S95" s="5"/>
       <c r="T95" s="1"/>
       <c r="U95" s="1">
-        <f t="shared" si="16"/>
-        <v>28.231707317073173</v>
-      </c>
-      <c r="V95" s="1">
         <f t="shared" si="17"/>
         <v>28.231707317073173</v>
       </c>
+      <c r="V95" s="1">
+        <f t="shared" si="18"/>
+        <v>28.231707317073173</v>
+      </c>
       <c r="W95" s="1">
         <v>39</v>
       </c>
@@ -10590,10 +10849,13 @@
         <v>36</v>
       </c>
       <c r="AC95" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AD95" s="1"/>
+      <c r="AD95" s="1">
+        <f t="shared" si="19"/>
+        <v>4.919999999999999</v>
+      </c>
       <c r="AE95" s="1"/>
       <c r="AF95" s="1"/>
       <c r="AG95" s="1"/>
@@ -10615,7 +10877,7 @@
       <c r="AW95" s="1"/>
       <c r="AX95" s="1"/>
     </row>
-    <row r="96" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>130</v>
       </c>
@@ -10648,7 +10910,7 @@
         <v>178</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-86</v>
       </c>
       <c r="M96" s="1"/>
@@ -10660,20 +10922,20 @@
         <v>192.5</v>
       </c>
       <c r="Q96" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>18.399999999999999</v>
       </c>
       <c r="R96" s="5"/>
       <c r="S96" s="5"/>
       <c r="T96" s="1"/>
       <c r="U96" s="1">
-        <f t="shared" si="16"/>
-        <v>20.217391304347828</v>
-      </c>
-      <c r="V96" s="1">
         <f t="shared" si="17"/>
         <v>20.217391304347828</v>
       </c>
+      <c r="V96" s="1">
+        <f t="shared" si="18"/>
+        <v>20.217391304347828</v>
+      </c>
       <c r="W96" s="1">
         <v>33.799999999999997</v>
       </c>
@@ -10691,10 +10953,13 @@
       </c>
       <c r="AB96" s="17"/>
       <c r="AC96" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AD96" s="1"/>
+      <c r="AD96" s="1">
+        <f t="shared" si="19"/>
+        <v>2.2079999999999997</v>
+      </c>
       <c r="AE96" s="1"/>
       <c r="AF96" s="1"/>
       <c r="AG96" s="1"/>
@@ -10716,7 +10981,7 @@
       <c r="AW96" s="1"/>
       <c r="AX96" s="1"/>
     </row>
-    <row r="97" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>125</v>
       </c>
@@ -10748,7 +11013,7 @@
         <v>185</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-70</v>
       </c>
       <c r="M97" s="1"/>
@@ -10760,20 +11025,20 @@
         <v>15</v>
       </c>
       <c r="Q97" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="R97" s="5"/>
       <c r="S97" s="5"/>
       <c r="T97" s="1"/>
       <c r="U97" s="1">
-        <f t="shared" si="16"/>
-        <v>17.739130434782609</v>
-      </c>
-      <c r="V97" s="1">
         <f t="shared" si="17"/>
         <v>17.739130434782609</v>
       </c>
+      <c r="V97" s="1">
+        <f t="shared" si="18"/>
+        <v>17.739130434782609</v>
+      </c>
       <c r="W97" s="1">
         <v>38</v>
       </c>
@@ -10791,10 +11056,13 @@
       </c>
       <c r="AB97" s="17"/>
       <c r="AC97" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AD97" s="1"/>
+      <c r="AD97" s="1">
+        <f t="shared" si="19"/>
+        <v>7.5900000000000007</v>
+      </c>
       <c r="AE97" s="1"/>
       <c r="AF97" s="1"/>
       <c r="AG97" s="1"/>
@@ -10816,7 +11084,7 @@
       <c r="AW97" s="1"/>
       <c r="AX97" s="1"/>
     </row>
-    <row r="98" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
         <v>131</v>
       </c>
@@ -10845,7 +11113,7 @@
         <v>3</v>
       </c>
       <c r="L98" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-2</v>
       </c>
       <c r="M98" s="10"/>
@@ -10853,20 +11121,20 @@
       <c r="O98" s="10"/>
       <c r="P98" s="10"/>
       <c r="Q98" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.2</v>
       </c>
       <c r="R98" s="12"/>
       <c r="S98" s="12"/>
       <c r="T98" s="10"/>
       <c r="U98" s="10">
-        <f t="shared" si="16"/>
-        <v>-5</v>
-      </c>
-      <c r="V98" s="10">
         <f t="shared" si="17"/>
         <v>-5</v>
       </c>
+      <c r="V98" s="10">
+        <f t="shared" si="18"/>
+        <v>-5</v>
+      </c>
       <c r="W98" s="10">
         <v>0</v>
       </c>
@@ -10884,7 +11152,10 @@
       </c>
       <c r="AB98" s="19"/>
       <c r="AC98" s="10"/>
-      <c r="AD98" s="1"/>
+      <c r="AD98" s="1">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
       <c r="AE98" s="1"/>
       <c r="AF98" s="1"/>
       <c r="AG98" s="1"/>
@@ -10906,7 +11177,7 @@
       <c r="AW98" s="1"/>
       <c r="AX98" s="1"/>
     </row>
-    <row r="99" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>133</v>
       </c>
@@ -10937,7 +11208,7 @@
         <v>83</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-4</v>
       </c>
       <c r="M99" s="1"/>
@@ -10949,11 +11220,11 @@
         <v>0</v>
       </c>
       <c r="Q99" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>15.8</v>
       </c>
       <c r="R99" s="5">
-        <f t="shared" ref="R99:R100" si="20">14*Q99-P99-O99-F99</f>
+        <f t="shared" ref="R99:R100" si="22">14*Q99-P99-O99-F99</f>
         <v>66.200000000000017</v>
       </c>
       <c r="S99" s="5">
@@ -10961,11 +11232,11 @@
       </c>
       <c r="T99" s="1"/>
       <c r="U99" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14</v>
       </c>
       <c r="V99" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>9.81012658227848</v>
       </c>
       <c r="W99" s="1">
@@ -10988,7 +11259,10 @@
         <f>G99*R99</f>
         <v>18.536000000000005</v>
       </c>
-      <c r="AD99" s="1"/>
+      <c r="AD99" s="1">
+        <f t="shared" si="19"/>
+        <v>4.4240000000000004</v>
+      </c>
       <c r="AE99" s="1"/>
       <c r="AF99" s="1"/>
       <c r="AG99" s="1"/>
@@ -11010,7 +11284,7 @@
       <c r="AW99" s="1"/>
       <c r="AX99" s="1"/>
     </row>
-    <row r="100" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>134</v>
       </c>
@@ -11041,7 +11315,7 @@
         <v>123</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-12</v>
       </c>
       <c r="M100" s="1"/>
@@ -11053,11 +11327,11 @@
         <v>82</v>
       </c>
       <c r="Q100" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>22.2</v>
       </c>
       <c r="R100" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>135.80000000000001</v>
       </c>
       <c r="S100" s="5">
@@ -11065,11 +11339,11 @@
       </c>
       <c r="T100" s="1"/>
       <c r="U100" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14.000000000000002</v>
       </c>
       <c r="V100" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7.8828828828828827</v>
       </c>
       <c r="W100" s="1">
@@ -11092,7 +11366,10 @@
         <f>G100*R100</f>
         <v>54.320000000000007</v>
       </c>
-      <c r="AD100" s="1"/>
+      <c r="AD100" s="1">
+        <f t="shared" si="19"/>
+        <v>8.8800000000000008</v>
+      </c>
       <c r="AE100" s="1"/>
       <c r="AF100" s="1"/>
       <c r="AG100" s="1"/>
@@ -11114,7 +11391,7 @@
       <c r="AW100" s="1"/>
       <c r="AX100" s="1"/>
     </row>
-    <row r="101" spans="1:50" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:50" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>132</v>
       </c>
@@ -11147,7 +11424,7 @@
         <v>2</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="M101" s="1"/>
@@ -11159,18 +11436,18 @@
         <v>25</v>
       </c>
       <c r="Q101" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.8</v>
       </c>
       <c r="R101" s="5"/>
       <c r="S101" s="5"/>
       <c r="T101" s="1"/>
       <c r="U101" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>174.44444444444443</v>
       </c>
       <c r="V101" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>174.44444444444443</v>
       </c>
       <c r="W101" s="1">
@@ -11195,7 +11472,10 @@
         <f>G101*R101</f>
         <v>0</v>
       </c>
-      <c r="AD101" s="1"/>
+      <c r="AD101" s="1">
+        <f t="shared" si="19"/>
+        <v>0.63</v>
+      </c>
       <c r="AE101" s="1"/>
       <c r="AF101" s="1"/>
       <c r="AG101" s="1"/>
@@ -11217,7 +11497,7 @@
       <c r="AW101" s="1"/>
       <c r="AX101" s="1"/>
     </row>
-    <row r="102" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>135</v>
       </c>
@@ -11250,7 +11530,7 @@
         <v>3.7</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L106" si="21">E102-K102</f>
+        <f t="shared" ref="L102:L106" si="23">E102-K102</f>
         <v>8.1840000000000011</v>
       </c>
       <c r="M102" s="1"/>
@@ -11262,18 +11542,18 @@
         <v>0</v>
       </c>
       <c r="Q102" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.3768000000000002</v>
       </c>
       <c r="R102" s="5"/>
       <c r="S102" s="5"/>
       <c r="T102" s="1"/>
       <c r="U102" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>48.526590373611569</v>
       </c>
       <c r="V102" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>48.526590373611569</v>
       </c>
       <c r="W102" s="1">
@@ -11296,7 +11576,10 @@
         <f>G102*R102</f>
         <v>0</v>
       </c>
-      <c r="AD102" s="1"/>
+      <c r="AD102" s="1">
+        <f t="shared" si="19"/>
+        <v>2.3768000000000002</v>
+      </c>
       <c r="AE102" s="1"/>
       <c r="AF102" s="1"/>
       <c r="AG102" s="1"/>
@@ -11318,7 +11601,7 @@
       <c r="AW102" s="1"/>
       <c r="AX102" s="1"/>
     </row>
-    <row r="103" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>136</v>
       </c>
@@ -11351,7 +11634,7 @@
         <v>10</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>80</v>
       </c>
       <c r="M103" s="1"/>
@@ -11363,18 +11646,18 @@
         <v>0</v>
       </c>
       <c r="Q103" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>18</v>
       </c>
       <c r="R103" s="5"/>
       <c r="S103" s="5"/>
       <c r="T103" s="1"/>
       <c r="U103" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>37</v>
       </c>
       <c r="V103" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>37</v>
       </c>
       <c r="W103" s="1">
@@ -11397,7 +11680,10 @@
         <f>G103*R103</f>
         <v>0</v>
       </c>
-      <c r="AD103" s="1"/>
+      <c r="AD103" s="1">
+        <f t="shared" si="19"/>
+        <v>5.94</v>
+      </c>
       <c r="AE103" s="1"/>
       <c r="AF103" s="1"/>
       <c r="AG103" s="1"/>
@@ -11419,7 +11705,7 @@
       <c r="AW103" s="1"/>
       <c r="AX103" s="1"/>
     </row>
-    <row r="104" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
         <v>137</v>
       </c>
@@ -11448,7 +11734,7 @@
         <v>26.6</v>
       </c>
       <c r="L104" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-25.261000000000003</v>
       </c>
       <c r="M104" s="10"/>
@@ -11460,20 +11746,20 @@
         <v>0</v>
       </c>
       <c r="Q104" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.26779999999999998</v>
       </c>
       <c r="R104" s="12"/>
       <c r="S104" s="12"/>
       <c r="T104" s="10"/>
       <c r="U104" s="10">
-        <f t="shared" si="16"/>
-        <v>-10.048543689320388</v>
-      </c>
-      <c r="V104" s="10">
         <f t="shared" si="17"/>
         <v>-10.048543689320388</v>
       </c>
+      <c r="V104" s="10">
+        <f t="shared" si="18"/>
+        <v>-10.048543689320388</v>
+      </c>
       <c r="W104" s="10">
         <v>0.27039999999999997</v>
       </c>
@@ -11491,7 +11777,10 @@
       </c>
       <c r="AB104" s="19"/>
       <c r="AC104" s="10"/>
-      <c r="AD104" s="1"/>
+      <c r="AD104" s="1">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
       <c r="AE104" s="1"/>
       <c r="AF104" s="1"/>
       <c r="AG104" s="1"/>
@@ -11513,7 +11802,7 @@
       <c r="AW104" s="1"/>
       <c r="AX104" s="1"/>
     </row>
-    <row r="105" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
         <v>139</v>
       </c>
@@ -11538,7 +11827,7 @@
       <c r="J105" s="10"/>
       <c r="K105" s="10"/>
       <c r="L105" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M105" s="10"/>
@@ -11550,20 +11839,20 @@
         <v>0</v>
       </c>
       <c r="Q105" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="R105" s="12"/>
       <c r="S105" s="12"/>
       <c r="T105" s="10"/>
       <c r="U105" s="10" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V105" s="10" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V105" s="10" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W105" s="10">
         <v>0.50940000000000007</v>
       </c>
@@ -11581,7 +11870,10 @@
       </c>
       <c r="AB105" s="19"/>
       <c r="AC105" s="10"/>
-      <c r="AD105" s="1"/>
+      <c r="AD105" s="1">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
       <c r="AE105" s="1"/>
       <c r="AF105" s="1"/>
       <c r="AG105" s="1"/>
@@ -11603,7 +11895,7 @@
       <c r="AW105" s="1"/>
       <c r="AX105" s="1"/>
     </row>
-    <row r="106" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
         <v>140</v>
       </c>
@@ -11632,7 +11924,7 @@
         <v>3</v>
       </c>
       <c r="L106" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-3</v>
       </c>
       <c r="M106" s="10"/>
@@ -11644,20 +11936,20 @@
         <v>0</v>
       </c>
       <c r="Q106" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="R106" s="12"/>
       <c r="S106" s="12"/>
       <c r="T106" s="10"/>
       <c r="U106" s="10" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V106" s="10" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V106" s="10" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W106" s="10">
         <v>0</v>
       </c>
@@ -11675,7 +11967,10 @@
       </c>
       <c r="AB106" s="19"/>
       <c r="AC106" s="10"/>
-      <c r="AD106" s="1"/>
+      <c r="AD106" s="1">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
       <c r="AE106" s="1"/>
       <c r="AF106" s="1"/>
       <c r="AG106" s="1"/>
@@ -11697,7 +11992,7 @@
       <c r="AW106" s="1"/>
       <c r="AX106" s="1"/>
     </row>
-    <row r="107" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -11749,7 +12044,7 @@
       <c r="AW107" s="1"/>
       <c r="AX107" s="1"/>
     </row>
-    <row r="108" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -11801,7 +12096,7 @@
       <c r="AW108" s="1"/>
       <c r="AX108" s="1"/>
     </row>
-    <row r="109" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -11853,7 +12148,7 @@
       <c r="AW109" s="1"/>
       <c r="AX109" s="1"/>
     </row>
-    <row r="110" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -11905,7 +12200,7 @@
       <c r="AW110" s="1"/>
       <c r="AX110" s="1"/>
     </row>
-    <row r="111" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -11957,7 +12252,7 @@
       <c r="AW111" s="1"/>
       <c r="AX111" s="1"/>
     </row>
-    <row r="112" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -12009,7 +12304,7 @@
       <c r="AW112" s="1"/>
       <c r="AX112" s="1"/>
     </row>
-    <row r="113" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -12061,7 +12356,7 @@
       <c r="AW113" s="1"/>
       <c r="AX113" s="1"/>
     </row>
-    <row r="114" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -12113,7 +12408,7 @@
       <c r="AW114" s="1"/>
       <c r="AX114" s="1"/>
     </row>
-    <row r="115" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -12165,7 +12460,7 @@
       <c r="AW115" s="1"/>
       <c r="AX115" s="1"/>
     </row>
-    <row r="116" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -12217,7 +12512,7 @@
       <c r="AW116" s="1"/>
       <c r="AX116" s="1"/>
     </row>
-    <row r="117" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -12269,7 +12564,7 @@
       <c r="AW117" s="1"/>
       <c r="AX117" s="1"/>
     </row>
-    <row r="118" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -12321,7 +12616,7 @@
       <c r="AW118" s="1"/>
       <c r="AX118" s="1"/>
     </row>
-    <row r="119" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -12373,7 +12668,7 @@
       <c r="AW119" s="1"/>
       <c r="AX119" s="1"/>
     </row>
-    <row r="120" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -12425,7 +12720,7 @@
       <c r="AW120" s="1"/>
       <c r="AX120" s="1"/>
     </row>
-    <row r="121" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -12477,7 +12772,7 @@
       <c r="AW121" s="1"/>
       <c r="AX121" s="1"/>
     </row>
-    <row r="122" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -12529,7 +12824,7 @@
       <c r="AW122" s="1"/>
       <c r="AX122" s="1"/>
     </row>
-    <row r="123" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -12581,7 +12876,7 @@
       <c r="AW123" s="1"/>
       <c r="AX123" s="1"/>
     </row>
-    <row r="124" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -12633,7 +12928,7 @@
       <c r="AW124" s="1"/>
       <c r="AX124" s="1"/>
     </row>
-    <row r="125" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -12685,7 +12980,7 @@
       <c r="AW125" s="1"/>
       <c r="AX125" s="1"/>
     </row>
-    <row r="126" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -12737,7 +13032,7 @@
       <c r="AW126" s="1"/>
       <c r="AX126" s="1"/>
     </row>
-    <row r="127" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -12789,7 +13084,7 @@
       <c r="AW127" s="1"/>
       <c r="AX127" s="1"/>
     </row>
-    <row r="128" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -12841,7 +13136,7 @@
       <c r="AW128" s="1"/>
       <c r="AX128" s="1"/>
     </row>
-    <row r="129" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -12893,7 +13188,7 @@
       <c r="AW129" s="1"/>
       <c r="AX129" s="1"/>
     </row>
-    <row r="130" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -12945,7 +13240,7 @@
       <c r="AW130" s="1"/>
       <c r="AX130" s="1"/>
     </row>
-    <row r="131" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -12997,7 +13292,7 @@
       <c r="AW131" s="1"/>
       <c r="AX131" s="1"/>
     </row>
-    <row r="132" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -13049,7 +13344,7 @@
       <c r="AW132" s="1"/>
       <c r="AX132" s="1"/>
     </row>
-    <row r="133" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -13101,7 +13396,7 @@
       <c r="AW133" s="1"/>
       <c r="AX133" s="1"/>
     </row>
-    <row r="134" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -13153,7 +13448,7 @@
       <c r="AW134" s="1"/>
       <c r="AX134" s="1"/>
     </row>
-    <row r="135" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -13205,7 +13500,7 @@
       <c r="AW135" s="1"/>
       <c r="AX135" s="1"/>
     </row>
-    <row r="136" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -13257,7 +13552,7 @@
       <c r="AW136" s="1"/>
       <c r="AX136" s="1"/>
     </row>
-    <row r="137" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -13309,7 +13604,7 @@
       <c r="AW137" s="1"/>
       <c r="AX137" s="1"/>
     </row>
-    <row r="138" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -13361,7 +13656,7 @@
       <c r="AW138" s="1"/>
       <c r="AX138" s="1"/>
     </row>
-    <row r="139" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -13413,7 +13708,7 @@
       <c r="AW139" s="1"/>
       <c r="AX139" s="1"/>
     </row>
-    <row r="140" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -13465,7 +13760,7 @@
       <c r="AW140" s="1"/>
       <c r="AX140" s="1"/>
     </row>
-    <row r="141" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -13517,7 +13812,7 @@
       <c r="AW141" s="1"/>
       <c r="AX141" s="1"/>
     </row>
-    <row r="142" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -13569,7 +13864,7 @@
       <c r="AW142" s="1"/>
       <c r="AX142" s="1"/>
     </row>
-    <row r="143" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -13621,7 +13916,7 @@
       <c r="AW143" s="1"/>
       <c r="AX143" s="1"/>
     </row>
-    <row r="144" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -13673,7 +13968,7 @@
       <c r="AW144" s="1"/>
       <c r="AX144" s="1"/>
     </row>
-    <row r="145" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -13725,7 +14020,7 @@
       <c r="AW145" s="1"/>
       <c r="AX145" s="1"/>
     </row>
-    <row r="146" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -13777,7 +14072,7 @@
       <c r="AW146" s="1"/>
       <c r="AX146" s="1"/>
     </row>
-    <row r="147" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -13829,7 +14124,7 @@
       <c r="AW147" s="1"/>
       <c r="AX147" s="1"/>
     </row>
-    <row r="148" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -13881,7 +14176,7 @@
       <c r="AW148" s="1"/>
       <c r="AX148" s="1"/>
     </row>
-    <row r="149" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -13933,7 +14228,7 @@
       <c r="AW149" s="1"/>
       <c r="AX149" s="1"/>
     </row>
-    <row r="150" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -13985,7 +14280,7 @@
       <c r="AW150" s="1"/>
       <c r="AX150" s="1"/>
     </row>
-    <row r="151" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -14037,7 +14332,7 @@
       <c r="AW151" s="1"/>
       <c r="AX151" s="1"/>
     </row>
-    <row r="152" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -14089,7 +14384,7 @@
       <c r="AW152" s="1"/>
       <c r="AX152" s="1"/>
     </row>
-    <row r="153" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -14141,7 +14436,7 @@
       <c r="AW153" s="1"/>
       <c r="AX153" s="1"/>
     </row>
-    <row r="154" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -14193,7 +14488,7 @@
       <c r="AW154" s="1"/>
       <c r="AX154" s="1"/>
     </row>
-    <row r="155" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -14245,7 +14540,7 @@
       <c r="AW155" s="1"/>
       <c r="AX155" s="1"/>
     </row>
-    <row r="156" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -14297,7 +14592,7 @@
       <c r="AW156" s="1"/>
       <c r="AX156" s="1"/>
     </row>
-    <row r="157" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -14349,7 +14644,7 @@
       <c r="AW157" s="1"/>
       <c r="AX157" s="1"/>
     </row>
-    <row r="158" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -14401,7 +14696,7 @@
       <c r="AW158" s="1"/>
       <c r="AX158" s="1"/>
     </row>
-    <row r="159" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -14453,7 +14748,7 @@
       <c r="AW159" s="1"/>
       <c r="AX159" s="1"/>
     </row>
-    <row r="160" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -14505,7 +14800,7 @@
       <c r="AW160" s="1"/>
       <c r="AX160" s="1"/>
     </row>
-    <row r="161" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -14557,7 +14852,7 @@
       <c r="AW161" s="1"/>
       <c r="AX161" s="1"/>
     </row>
-    <row r="162" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -14609,7 +14904,7 @@
       <c r="AW162" s="1"/>
       <c r="AX162" s="1"/>
     </row>
-    <row r="163" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -14661,7 +14956,7 @@
       <c r="AW163" s="1"/>
       <c r="AX163" s="1"/>
     </row>
-    <row r="164" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -14713,7 +15008,7 @@
       <c r="AW164" s="1"/>
       <c r="AX164" s="1"/>
     </row>
-    <row r="165" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -14765,7 +15060,7 @@
       <c r="AW165" s="1"/>
       <c r="AX165" s="1"/>
     </row>
-    <row r="166" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -14817,7 +15112,7 @@
       <c r="AW166" s="1"/>
       <c r="AX166" s="1"/>
     </row>
-    <row r="167" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -14869,7 +15164,7 @@
       <c r="AW167" s="1"/>
       <c r="AX167" s="1"/>
     </row>
-    <row r="168" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -14921,7 +15216,7 @@
       <c r="AW168" s="1"/>
       <c r="AX168" s="1"/>
     </row>
-    <row r="169" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -14973,7 +15268,7 @@
       <c r="AW169" s="1"/>
       <c r="AX169" s="1"/>
     </row>
-    <row r="170" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -15025,7 +15320,7 @@
       <c r="AW170" s="1"/>
       <c r="AX170" s="1"/>
     </row>
-    <row r="171" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -15077,7 +15372,7 @@
       <c r="AW171" s="1"/>
       <c r="AX171" s="1"/>
     </row>
-    <row r="172" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -15129,7 +15424,7 @@
       <c r="AW172" s="1"/>
       <c r="AX172" s="1"/>
     </row>
-    <row r="173" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -15181,7 +15476,7 @@
       <c r="AW173" s="1"/>
       <c r="AX173" s="1"/>
     </row>
-    <row r="174" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -15233,7 +15528,7 @@
       <c r="AW174" s="1"/>
       <c r="AX174" s="1"/>
     </row>
-    <row r="175" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -15285,7 +15580,7 @@
       <c r="AW175" s="1"/>
       <c r="AX175" s="1"/>
     </row>
-    <row r="176" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -15337,7 +15632,7 @@
       <c r="AW176" s="1"/>
       <c r="AX176" s="1"/>
     </row>
-    <row r="177" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -15389,7 +15684,7 @@
       <c r="AW177" s="1"/>
       <c r="AX177" s="1"/>
     </row>
-    <row r="178" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -15441,7 +15736,7 @@
       <c r="AW178" s="1"/>
       <c r="AX178" s="1"/>
     </row>
-    <row r="179" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -15493,7 +15788,7 @@
       <c r="AW179" s="1"/>
       <c r="AX179" s="1"/>
     </row>
-    <row r="180" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -15545,7 +15840,7 @@
       <c r="AW180" s="1"/>
       <c r="AX180" s="1"/>
     </row>
-    <row r="181" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -15597,7 +15892,7 @@
       <c r="AW181" s="1"/>
       <c r="AX181" s="1"/>
     </row>
-    <row r="182" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -15649,7 +15944,7 @@
       <c r="AW182" s="1"/>
       <c r="AX182" s="1"/>
     </row>
-    <row r="183" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -15701,7 +15996,7 @@
       <c r="AW183" s="1"/>
       <c r="AX183" s="1"/>
     </row>
-    <row r="184" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -15753,7 +16048,7 @@
       <c r="AW184" s="1"/>
       <c r="AX184" s="1"/>
     </row>
-    <row r="185" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -15805,7 +16100,7 @@
       <c r="AW185" s="1"/>
       <c r="AX185" s="1"/>
     </row>
-    <row r="186" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -15857,7 +16152,7 @@
       <c r="AW186" s="1"/>
       <c r="AX186" s="1"/>
     </row>
-    <row r="187" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -15909,7 +16204,7 @@
       <c r="AW187" s="1"/>
       <c r="AX187" s="1"/>
     </row>
-    <row r="188" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -15961,7 +16256,7 @@
       <c r="AW188" s="1"/>
       <c r="AX188" s="1"/>
     </row>
-    <row r="189" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -16013,7 +16308,7 @@
       <c r="AW189" s="1"/>
       <c r="AX189" s="1"/>
     </row>
-    <row r="190" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -16065,7 +16360,7 @@
       <c r="AW190" s="1"/>
       <c r="AX190" s="1"/>
     </row>
-    <row r="191" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -16117,7 +16412,7 @@
       <c r="AW191" s="1"/>
       <c r="AX191" s="1"/>
     </row>
-    <row r="192" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -16169,7 +16464,7 @@
       <c r="AW192" s="1"/>
       <c r="AX192" s="1"/>
     </row>
-    <row r="193" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -16221,7 +16516,7 @@
       <c r="AW193" s="1"/>
       <c r="AX193" s="1"/>
     </row>
-    <row r="194" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -16273,7 +16568,7 @@
       <c r="AW194" s="1"/>
       <c r="AX194" s="1"/>
     </row>
-    <row r="195" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -16325,7 +16620,7 @@
       <c r="AW195" s="1"/>
       <c r="AX195" s="1"/>
     </row>
-    <row r="196" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -16377,7 +16672,7 @@
       <c r="AW196" s="1"/>
       <c r="AX196" s="1"/>
     </row>
-    <row r="197" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -16429,7 +16724,7 @@
       <c r="AW197" s="1"/>
       <c r="AX197" s="1"/>
     </row>
-    <row r="198" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -16481,7 +16776,7 @@
       <c r="AW198" s="1"/>
       <c r="AX198" s="1"/>
     </row>
-    <row r="199" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -16533,7 +16828,7 @@
       <c r="AW199" s="1"/>
       <c r="AX199" s="1"/>
     </row>
-    <row r="200" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -16585,7 +16880,7 @@
       <c r="AW200" s="1"/>
       <c r="AX200" s="1"/>
     </row>
-    <row r="201" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -16637,7 +16932,7 @@
       <c r="AW201" s="1"/>
       <c r="AX201" s="1"/>
     </row>
-    <row r="202" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -16689,7 +16984,7 @@
       <c r="AW202" s="1"/>
       <c r="AX202" s="1"/>
     </row>
-    <row r="203" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -16741,7 +17036,7 @@
       <c r="AW203" s="1"/>
       <c r="AX203" s="1"/>
     </row>
-    <row r="204" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -16793,7 +17088,7 @@
       <c r="AW204" s="1"/>
       <c r="AX204" s="1"/>
     </row>
-    <row r="205" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -16845,7 +17140,7 @@
       <c r="AW205" s="1"/>
       <c r="AX205" s="1"/>
     </row>
-    <row r="206" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -16897,7 +17192,7 @@
       <c r="AW206" s="1"/>
       <c r="AX206" s="1"/>
     </row>
-    <row r="207" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -16949,7 +17244,7 @@
       <c r="AW207" s="1"/>
       <c r="AX207" s="1"/>
     </row>
-    <row r="208" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -17001,7 +17296,7 @@
       <c r="AW208" s="1"/>
       <c r="AX208" s="1"/>
     </row>
-    <row r="209" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -17053,7 +17348,7 @@
       <c r="AW209" s="1"/>
       <c r="AX209" s="1"/>
     </row>
-    <row r="210" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -17105,7 +17400,7 @@
       <c r="AW210" s="1"/>
       <c r="AX210" s="1"/>
     </row>
-    <row r="211" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -17157,7 +17452,7 @@
       <c r="AW211" s="1"/>
       <c r="AX211" s="1"/>
     </row>
-    <row r="212" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -17209,7 +17504,7 @@
       <c r="AW212" s="1"/>
       <c r="AX212" s="1"/>
     </row>
-    <row r="213" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -17261,7 +17556,7 @@
       <c r="AW213" s="1"/>
       <c r="AX213" s="1"/>
     </row>
-    <row r="214" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -17313,7 +17608,7 @@
       <c r="AW214" s="1"/>
       <c r="AX214" s="1"/>
     </row>
-    <row r="215" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -17365,7 +17660,7 @@
       <c r="AW215" s="1"/>
       <c r="AX215" s="1"/>
     </row>
-    <row r="216" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -17417,7 +17712,7 @@
       <c r="AW216" s="1"/>
       <c r="AX216" s="1"/>
     </row>
-    <row r="217" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -17469,7 +17764,7 @@
       <c r="AW217" s="1"/>
       <c r="AX217" s="1"/>
     </row>
-    <row r="218" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -17521,7 +17816,7 @@
       <c r="AW218" s="1"/>
       <c r="AX218" s="1"/>
     </row>
-    <row r="219" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -17573,7 +17868,7 @@
       <c r="AW219" s="1"/>
       <c r="AX219" s="1"/>
     </row>
-    <row r="220" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -17625,7 +17920,7 @@
       <c r="AW220" s="1"/>
       <c r="AX220" s="1"/>
     </row>
-    <row r="221" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -17677,7 +17972,7 @@
       <c r="AW221" s="1"/>
       <c r="AX221" s="1"/>
     </row>
-    <row r="222" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -17729,7 +18024,7 @@
       <c r="AW222" s="1"/>
       <c r="AX222" s="1"/>
     </row>
-    <row r="223" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -17781,7 +18076,7 @@
       <c r="AW223" s="1"/>
       <c r="AX223" s="1"/>
     </row>
-    <row r="224" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -17833,7 +18128,7 @@
       <c r="AW224" s="1"/>
       <c r="AX224" s="1"/>
     </row>
-    <row r="225" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -17885,7 +18180,7 @@
       <c r="AW225" s="1"/>
       <c r="AX225" s="1"/>
     </row>
-    <row r="226" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -17937,7 +18232,7 @@
       <c r="AW226" s="1"/>
       <c r="AX226" s="1"/>
     </row>
-    <row r="227" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -17989,7 +18284,7 @@
       <c r="AW227" s="1"/>
       <c r="AX227" s="1"/>
     </row>
-    <row r="228" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -18041,7 +18336,7 @@
       <c r="AW228" s="1"/>
       <c r="AX228" s="1"/>
     </row>
-    <row r="229" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -18093,7 +18388,7 @@
       <c r="AW229" s="1"/>
       <c r="AX229" s="1"/>
     </row>
-    <row r="230" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -18145,7 +18440,7 @@
       <c r="AW230" s="1"/>
       <c r="AX230" s="1"/>
     </row>
-    <row r="231" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -18197,7 +18492,7 @@
       <c r="AW231" s="1"/>
       <c r="AX231" s="1"/>
     </row>
-    <row r="232" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -18249,7 +18544,7 @@
       <c r="AW232" s="1"/>
       <c r="AX232" s="1"/>
     </row>
-    <row r="233" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -18301,7 +18596,7 @@
       <c r="AW233" s="1"/>
       <c r="AX233" s="1"/>
     </row>
-    <row r="234" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -18353,7 +18648,7 @@
       <c r="AW234" s="1"/>
       <c r="AX234" s="1"/>
     </row>
-    <row r="235" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -18405,7 +18700,7 @@
       <c r="AW235" s="1"/>
       <c r="AX235" s="1"/>
     </row>
-    <row r="236" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -18457,7 +18752,7 @@
       <c r="AW236" s="1"/>
       <c r="AX236" s="1"/>
     </row>
-    <row r="237" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -18509,7 +18804,7 @@
       <c r="AW237" s="1"/>
       <c r="AX237" s="1"/>
     </row>
-    <row r="238" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -18561,7 +18856,7 @@
       <c r="AW238" s="1"/>
       <c r="AX238" s="1"/>
     </row>
-    <row r="239" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -18613,7 +18908,7 @@
       <c r="AW239" s="1"/>
       <c r="AX239" s="1"/>
     </row>
-    <row r="240" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -18665,7 +18960,7 @@
       <c r="AW240" s="1"/>
       <c r="AX240" s="1"/>
     </row>
-    <row r="241" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -18717,7 +19012,7 @@
       <c r="AW241" s="1"/>
       <c r="AX241" s="1"/>
     </row>
-    <row r="242" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -18769,7 +19064,7 @@
       <c r="AW242" s="1"/>
       <c r="AX242" s="1"/>
     </row>
-    <row r="243" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -18821,7 +19116,7 @@
       <c r="AW243" s="1"/>
       <c r="AX243" s="1"/>
     </row>
-    <row r="244" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -18873,7 +19168,7 @@
       <c r="AW244" s="1"/>
       <c r="AX244" s="1"/>
     </row>
-    <row r="245" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -18925,7 +19220,7 @@
       <c r="AW245" s="1"/>
       <c r="AX245" s="1"/>
     </row>
-    <row r="246" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -18977,7 +19272,7 @@
       <c r="AW246" s="1"/>
       <c r="AX246" s="1"/>
     </row>
-    <row r="247" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -19029,7 +19324,7 @@
       <c r="AW247" s="1"/>
       <c r="AX247" s="1"/>
     </row>
-    <row r="248" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -19081,7 +19376,7 @@
       <c r="AW248" s="1"/>
       <c r="AX248" s="1"/>
     </row>
-    <row r="249" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -19133,7 +19428,7 @@
       <c r="AW249" s="1"/>
       <c r="AX249" s="1"/>
     </row>
-    <row r="250" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -19185,7 +19480,7 @@
       <c r="AW250" s="1"/>
       <c r="AX250" s="1"/>
     </row>
-    <row r="251" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -19237,7 +19532,7 @@
       <c r="AW251" s="1"/>
       <c r="AX251" s="1"/>
     </row>
-    <row r="252" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -19289,7 +19584,7 @@
       <c r="AW252" s="1"/>
       <c r="AX252" s="1"/>
     </row>
-    <row r="253" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -19341,7 +19636,7 @@
       <c r="AW253" s="1"/>
       <c r="AX253" s="1"/>
     </row>
-    <row r="254" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -19393,7 +19688,7 @@
       <c r="AW254" s="1"/>
       <c r="AX254" s="1"/>
     </row>
-    <row r="255" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -19445,7 +19740,7 @@
       <c r="AW255" s="1"/>
       <c r="AX255" s="1"/>
     </row>
-    <row r="256" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -19497,7 +19792,7 @@
       <c r="AW256" s="1"/>
       <c r="AX256" s="1"/>
     </row>
-    <row r="257" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -19549,7 +19844,7 @@
       <c r="AW257" s="1"/>
       <c r="AX257" s="1"/>
     </row>
-    <row r="258" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -19601,7 +19896,7 @@
       <c r="AW258" s="1"/>
       <c r="AX258" s="1"/>
     </row>
-    <row r="259" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -19653,7 +19948,7 @@
       <c r="AW259" s="1"/>
       <c r="AX259" s="1"/>
     </row>
-    <row r="260" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -19705,7 +20000,7 @@
       <c r="AW260" s="1"/>
       <c r="AX260" s="1"/>
     </row>
-    <row r="261" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -19757,7 +20052,7 @@
       <c r="AW261" s="1"/>
       <c r="AX261" s="1"/>
     </row>
-    <row r="262" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -19809,7 +20104,7 @@
       <c r="AW262" s="1"/>
       <c r="AX262" s="1"/>
     </row>
-    <row r="263" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -19861,7 +20156,7 @@
       <c r="AW263" s="1"/>
       <c r="AX263" s="1"/>
     </row>
-    <row r="264" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -19913,7 +20208,7 @@
       <c r="AW264" s="1"/>
       <c r="AX264" s="1"/>
     </row>
-    <row r="265" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -19965,7 +20260,7 @@
       <c r="AW265" s="1"/>
       <c r="AX265" s="1"/>
     </row>
-    <row r="266" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -20017,7 +20312,7 @@
       <c r="AW266" s="1"/>
       <c r="AX266" s="1"/>
     </row>
-    <row r="267" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -20069,7 +20364,7 @@
       <c r="AW267" s="1"/>
       <c r="AX267" s="1"/>
     </row>
-    <row r="268" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -20121,7 +20416,7 @@
       <c r="AW268" s="1"/>
       <c r="AX268" s="1"/>
     </row>
-    <row r="269" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -20173,7 +20468,7 @@
       <c r="AW269" s="1"/>
       <c r="AX269" s="1"/>
     </row>
-    <row r="270" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -20225,7 +20520,7 @@
       <c r="AW270" s="1"/>
       <c r="AX270" s="1"/>
     </row>
-    <row r="271" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -20277,7 +20572,7 @@
       <c r="AW271" s="1"/>
       <c r="AX271" s="1"/>
     </row>
-    <row r="272" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -20329,7 +20624,7 @@
       <c r="AW272" s="1"/>
       <c r="AX272" s="1"/>
     </row>
-    <row r="273" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -20381,7 +20676,7 @@
       <c r="AW273" s="1"/>
       <c r="AX273" s="1"/>
     </row>
-    <row r="274" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -20433,7 +20728,7 @@
       <c r="AW274" s="1"/>
       <c r="AX274" s="1"/>
     </row>
-    <row r="275" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -20485,7 +20780,7 @@
       <c r="AW275" s="1"/>
       <c r="AX275" s="1"/>
     </row>
-    <row r="276" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -20537,7 +20832,7 @@
       <c r="AW276" s="1"/>
       <c r="AX276" s="1"/>
     </row>
-    <row r="277" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -20589,7 +20884,7 @@
       <c r="AW277" s="1"/>
       <c r="AX277" s="1"/>
     </row>
-    <row r="278" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -20641,7 +20936,7 @@
       <c r="AW278" s="1"/>
       <c r="AX278" s="1"/>
     </row>
-    <row r="279" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -20693,7 +20988,7 @@
       <c r="AW279" s="1"/>
       <c r="AX279" s="1"/>
     </row>
-    <row r="280" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -20745,7 +21040,7 @@
       <c r="AW280" s="1"/>
       <c r="AX280" s="1"/>
     </row>
-    <row r="281" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -20797,7 +21092,7 @@
       <c r="AW281" s="1"/>
       <c r="AX281" s="1"/>
     </row>
-    <row r="282" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -20849,7 +21144,7 @@
       <c r="AW282" s="1"/>
       <c r="AX282" s="1"/>
     </row>
-    <row r="283" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -20901,7 +21196,7 @@
       <c r="AW283" s="1"/>
       <c r="AX283" s="1"/>
     </row>
-    <row r="284" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -20953,7 +21248,7 @@
       <c r="AW284" s="1"/>
       <c r="AX284" s="1"/>
     </row>
-    <row r="285" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -21005,7 +21300,7 @@
       <c r="AW285" s="1"/>
       <c r="AX285" s="1"/>
     </row>
-    <row r="286" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -21057,7 +21352,7 @@
       <c r="AW286" s="1"/>
       <c r="AX286" s="1"/>
     </row>
-    <row r="287" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -21109,7 +21404,7 @@
       <c r="AW287" s="1"/>
       <c r="AX287" s="1"/>
     </row>
-    <row r="288" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -21161,7 +21456,7 @@
       <c r="AW288" s="1"/>
       <c r="AX288" s="1"/>
     </row>
-    <row r="289" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -21213,7 +21508,7 @@
       <c r="AW289" s="1"/>
       <c r="AX289" s="1"/>
     </row>
-    <row r="290" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -21265,7 +21560,7 @@
       <c r="AW290" s="1"/>
       <c r="AX290" s="1"/>
     </row>
-    <row r="291" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -21317,7 +21612,7 @@
       <c r="AW291" s="1"/>
       <c r="AX291" s="1"/>
     </row>
-    <row r="292" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -21369,7 +21664,7 @@
       <c r="AW292" s="1"/>
       <c r="AX292" s="1"/>
     </row>
-    <row r="293" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -21421,7 +21716,7 @@
       <c r="AW293" s="1"/>
       <c r="AX293" s="1"/>
     </row>
-    <row r="294" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -21473,7 +21768,7 @@
       <c r="AW294" s="1"/>
       <c r="AX294" s="1"/>
     </row>
-    <row r="295" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -21525,7 +21820,7 @@
       <c r="AW295" s="1"/>
       <c r="AX295" s="1"/>
     </row>
-    <row r="296" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -21577,7 +21872,7 @@
       <c r="AW296" s="1"/>
       <c r="AX296" s="1"/>
     </row>
-    <row r="297" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -21629,7 +21924,7 @@
       <c r="AW297" s="1"/>
       <c r="AX297" s="1"/>
     </row>
-    <row r="298" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -21681,7 +21976,7 @@
       <c r="AW298" s="1"/>
       <c r="AX298" s="1"/>
     </row>
-    <row r="299" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -21733,7 +22028,7 @@
       <c r="AW299" s="1"/>
       <c r="AX299" s="1"/>
     </row>
-    <row r="300" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -21785,7 +22080,7 @@
       <c r="AW300" s="1"/>
       <c r="AX300" s="1"/>
     </row>
-    <row r="301" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -21837,7 +22132,7 @@
       <c r="AW301" s="1"/>
       <c r="AX301" s="1"/>
     </row>
-    <row r="302" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -21889,7 +22184,7 @@
       <c r="AW302" s="1"/>
       <c r="AX302" s="1"/>
     </row>
-    <row r="303" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -21941,7 +22236,7 @@
       <c r="AW303" s="1"/>
       <c r="AX303" s="1"/>
     </row>
-    <row r="304" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -21993,7 +22288,7 @@
       <c r="AW304" s="1"/>
       <c r="AX304" s="1"/>
     </row>
-    <row r="305" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -22045,7 +22340,7 @@
       <c r="AW305" s="1"/>
       <c r="AX305" s="1"/>
     </row>
-    <row r="306" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -22097,7 +22392,7 @@
       <c r="AW306" s="1"/>
       <c r="AX306" s="1"/>
     </row>
-    <row r="307" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -22149,7 +22444,7 @@
       <c r="AW307" s="1"/>
       <c r="AX307" s="1"/>
     </row>
-    <row r="308" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -22201,7 +22496,7 @@
       <c r="AW308" s="1"/>
       <c r="AX308" s="1"/>
     </row>
-    <row r="309" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -22253,7 +22548,7 @@
       <c r="AW309" s="1"/>
       <c r="AX309" s="1"/>
     </row>
-    <row r="310" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -22305,7 +22600,7 @@
       <c r="AW310" s="1"/>
       <c r="AX310" s="1"/>
     </row>
-    <row r="311" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -22357,7 +22652,7 @@
       <c r="AW311" s="1"/>
       <c r="AX311" s="1"/>
     </row>
-    <row r="312" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -22409,7 +22704,7 @@
       <c r="AW312" s="1"/>
       <c r="AX312" s="1"/>
     </row>
-    <row r="313" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -22461,7 +22756,7 @@
       <c r="AW313" s="1"/>
       <c r="AX313" s="1"/>
     </row>
-    <row r="314" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -22513,7 +22808,7 @@
       <c r="AW314" s="1"/>
       <c r="AX314" s="1"/>
     </row>
-    <row r="315" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -22565,7 +22860,7 @@
       <c r="AW315" s="1"/>
       <c r="AX315" s="1"/>
     </row>
-    <row r="316" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -22617,7 +22912,7 @@
       <c r="AW316" s="1"/>
       <c r="AX316" s="1"/>
     </row>
-    <row r="317" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -22669,7 +22964,7 @@
       <c r="AW317" s="1"/>
       <c r="AX317" s="1"/>
     </row>
-    <row r="318" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -22721,7 +23016,7 @@
       <c r="AW318" s="1"/>
       <c r="AX318" s="1"/>
     </row>
-    <row r="319" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -22773,7 +23068,7 @@
       <c r="AW319" s="1"/>
       <c r="AX319" s="1"/>
     </row>
-    <row r="320" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -22825,7 +23120,7 @@
       <c r="AW320" s="1"/>
       <c r="AX320" s="1"/>
     </row>
-    <row r="321" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -22877,7 +23172,7 @@
       <c r="AW321" s="1"/>
       <c r="AX321" s="1"/>
     </row>
-    <row r="322" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -22929,7 +23224,7 @@
       <c r="AW322" s="1"/>
       <c r="AX322" s="1"/>
     </row>
-    <row r="323" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -22981,7 +23276,7 @@
       <c r="AW323" s="1"/>
       <c r="AX323" s="1"/>
     </row>
-    <row r="324" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -23033,7 +23328,7 @@
       <c r="AW324" s="1"/>
       <c r="AX324" s="1"/>
     </row>
-    <row r="325" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -23085,7 +23380,7 @@
       <c r="AW325" s="1"/>
       <c r="AX325" s="1"/>
     </row>
-    <row r="326" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -23137,7 +23432,7 @@
       <c r="AW326" s="1"/>
       <c r="AX326" s="1"/>
     </row>
-    <row r="327" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -23189,7 +23484,7 @@
       <c r="AW327" s="1"/>
       <c r="AX327" s="1"/>
     </row>
-    <row r="328" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -23241,7 +23536,7 @@
       <c r="AW328" s="1"/>
       <c r="AX328" s="1"/>
     </row>
-    <row r="329" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -23293,7 +23588,7 @@
       <c r="AW329" s="1"/>
       <c r="AX329" s="1"/>
     </row>
-    <row r="330" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -23345,7 +23640,7 @@
       <c r="AW330" s="1"/>
       <c r="AX330" s="1"/>
     </row>
-    <row r="331" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -23397,7 +23692,7 @@
       <c r="AW331" s="1"/>
       <c r="AX331" s="1"/>
     </row>
-    <row r="332" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -23449,7 +23744,7 @@
       <c r="AW332" s="1"/>
       <c r="AX332" s="1"/>
     </row>
-    <row r="333" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -23501,7 +23796,7 @@
       <c r="AW333" s="1"/>
       <c r="AX333" s="1"/>
     </row>
-    <row r="334" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -23553,7 +23848,7 @@
       <c r="AW334" s="1"/>
       <c r="AX334" s="1"/>
     </row>
-    <row r="335" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -23605,7 +23900,7 @@
       <c r="AW335" s="1"/>
       <c r="AX335" s="1"/>
     </row>
-    <row r="336" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -23657,7 +23952,7 @@
       <c r="AW336" s="1"/>
       <c r="AX336" s="1"/>
     </row>
-    <row r="337" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -23709,7 +24004,7 @@
       <c r="AW337" s="1"/>
       <c r="AX337" s="1"/>
     </row>
-    <row r="338" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -23761,7 +24056,7 @@
       <c r="AW338" s="1"/>
       <c r="AX338" s="1"/>
     </row>
-    <row r="339" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -23813,7 +24108,7 @@
       <c r="AW339" s="1"/>
       <c r="AX339" s="1"/>
     </row>
-    <row r="340" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -23865,7 +24160,7 @@
       <c r="AW340" s="1"/>
       <c r="AX340" s="1"/>
     </row>
-    <row r="341" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -23917,7 +24212,7 @@
       <c r="AW341" s="1"/>
       <c r="AX341" s="1"/>
     </row>
-    <row r="342" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -23969,7 +24264,7 @@
       <c r="AW342" s="1"/>
       <c r="AX342" s="1"/>
     </row>
-    <row r="343" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -24021,7 +24316,7 @@
       <c r="AW343" s="1"/>
       <c r="AX343" s="1"/>
     </row>
-    <row r="344" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -24073,7 +24368,7 @@
       <c r="AW344" s="1"/>
       <c r="AX344" s="1"/>
     </row>
-    <row r="345" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -24125,7 +24420,7 @@
       <c r="AW345" s="1"/>
       <c r="AX345" s="1"/>
     </row>
-    <row r="346" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -24177,7 +24472,7 @@
       <c r="AW346" s="1"/>
       <c r="AX346" s="1"/>
     </row>
-    <row r="347" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -24229,7 +24524,7 @@
       <c r="AW347" s="1"/>
       <c r="AX347" s="1"/>
     </row>
-    <row r="348" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -24281,7 +24576,7 @@
       <c r="AW348" s="1"/>
       <c r="AX348" s="1"/>
     </row>
-    <row r="349" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -24333,7 +24628,7 @@
       <c r="AW349" s="1"/>
       <c r="AX349" s="1"/>
     </row>
-    <row r="350" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -24385,7 +24680,7 @@
       <c r="AW350" s="1"/>
       <c r="AX350" s="1"/>
     </row>
-    <row r="351" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -24437,7 +24732,7 @@
       <c r="AW351" s="1"/>
       <c r="AX351" s="1"/>
     </row>
-    <row r="352" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -24489,7 +24784,7 @@
       <c r="AW352" s="1"/>
       <c r="AX352" s="1"/>
     </row>
-    <row r="353" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -24541,7 +24836,7 @@
       <c r="AW353" s="1"/>
       <c r="AX353" s="1"/>
     </row>
-    <row r="354" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -24593,7 +24888,7 @@
       <c r="AW354" s="1"/>
       <c r="AX354" s="1"/>
     </row>
-    <row r="355" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -24645,7 +24940,7 @@
       <c r="AW355" s="1"/>
       <c r="AX355" s="1"/>
     </row>
-    <row r="356" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -24697,7 +24992,7 @@
       <c r="AW356" s="1"/>
       <c r="AX356" s="1"/>
     </row>
-    <row r="357" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -24749,7 +25044,7 @@
       <c r="AW357" s="1"/>
       <c r="AX357" s="1"/>
     </row>
-    <row r="358" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -24801,7 +25096,7 @@
       <c r="AW358" s="1"/>
       <c r="AX358" s="1"/>
     </row>
-    <row r="359" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -24853,7 +25148,7 @@
       <c r="AW359" s="1"/>
       <c r="AX359" s="1"/>
     </row>
-    <row r="360" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -24905,7 +25200,7 @@
       <c r="AW360" s="1"/>
       <c r="AX360" s="1"/>
     </row>
-    <row r="361" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -24957,7 +25252,7 @@
       <c r="AW361" s="1"/>
       <c r="AX361" s="1"/>
     </row>
-    <row r="362" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -25009,7 +25304,7 @@
       <c r="AW362" s="1"/>
       <c r="AX362" s="1"/>
     </row>
-    <row r="363" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -25061,7 +25356,7 @@
       <c r="AW363" s="1"/>
       <c r="AX363" s="1"/>
     </row>
-    <row r="364" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -25113,7 +25408,7 @@
       <c r="AW364" s="1"/>
       <c r="AX364" s="1"/>
     </row>
-    <row r="365" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -25165,7 +25460,7 @@
       <c r="AW365" s="1"/>
       <c r="AX365" s="1"/>
     </row>
-    <row r="366" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -25217,7 +25512,7 @@
       <c r="AW366" s="1"/>
       <c r="AX366" s="1"/>
     </row>
-    <row r="367" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -25269,7 +25564,7 @@
       <c r="AW367" s="1"/>
       <c r="AX367" s="1"/>
     </row>
-    <row r="368" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -25321,7 +25616,7 @@
       <c r="AW368" s="1"/>
       <c r="AX368" s="1"/>
     </row>
-    <row r="369" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -25373,7 +25668,7 @@
       <c r="AW369" s="1"/>
       <c r="AX369" s="1"/>
     </row>
-    <row r="370" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -25425,7 +25720,7 @@
       <c r="AW370" s="1"/>
       <c r="AX370" s="1"/>
     </row>
-    <row r="371" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -25477,7 +25772,7 @@
       <c r="AW371" s="1"/>
       <c r="AX371" s="1"/>
     </row>
-    <row r="372" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -25529,7 +25824,7 @@
       <c r="AW372" s="1"/>
       <c r="AX372" s="1"/>
     </row>
-    <row r="373" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -25581,7 +25876,7 @@
       <c r="AW373" s="1"/>
       <c r="AX373" s="1"/>
     </row>
-    <row r="374" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -25633,7 +25928,7 @@
       <c r="AW374" s="1"/>
       <c r="AX374" s="1"/>
     </row>
-    <row r="375" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -25685,7 +25980,7 @@
       <c r="AW375" s="1"/>
       <c r="AX375" s="1"/>
     </row>
-    <row r="376" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -25737,7 +26032,7 @@
       <c r="AW376" s="1"/>
       <c r="AX376" s="1"/>
     </row>
-    <row r="377" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -25789,7 +26084,7 @@
       <c r="AW377" s="1"/>
       <c r="AX377" s="1"/>
     </row>
-    <row r="378" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -25841,7 +26136,7 @@
       <c r="AW378" s="1"/>
       <c r="AX378" s="1"/>
     </row>
-    <row r="379" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -25893,7 +26188,7 @@
       <c r="AW379" s="1"/>
       <c r="AX379" s="1"/>
     </row>
-    <row r="380" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -25945,7 +26240,7 @@
       <c r="AW380" s="1"/>
       <c r="AX380" s="1"/>
     </row>
-    <row r="381" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -25997,7 +26292,7 @@
       <c r="AW381" s="1"/>
       <c r="AX381" s="1"/>
     </row>
-    <row r="382" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -26049,7 +26344,7 @@
       <c r="AW382" s="1"/>
       <c r="AX382" s="1"/>
     </row>
-    <row r="383" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -26101,7 +26396,7 @@
       <c r="AW383" s="1"/>
       <c r="AX383" s="1"/>
     </row>
-    <row r="384" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -26153,7 +26448,7 @@
       <c r="AW384" s="1"/>
       <c r="AX384" s="1"/>
     </row>
-    <row r="385" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -26205,7 +26500,7 @@
       <c r="AW385" s="1"/>
       <c r="AX385" s="1"/>
     </row>
-    <row r="386" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -26257,7 +26552,7 @@
       <c r="AW386" s="1"/>
       <c r="AX386" s="1"/>
     </row>
-    <row r="387" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -26309,7 +26604,7 @@
       <c r="AW387" s="1"/>
       <c r="AX387" s="1"/>
     </row>
-    <row r="388" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -26361,7 +26656,7 @@
       <c r="AW388" s="1"/>
       <c r="AX388" s="1"/>
     </row>
-    <row r="389" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -26413,7 +26708,7 @@
       <c r="AW389" s="1"/>
       <c r="AX389" s="1"/>
     </row>
-    <row r="390" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -26465,7 +26760,7 @@
       <c r="AW390" s="1"/>
       <c r="AX390" s="1"/>
     </row>
-    <row r="391" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -26517,7 +26812,7 @@
       <c r="AW391" s="1"/>
       <c r="AX391" s="1"/>
     </row>
-    <row r="392" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -26569,7 +26864,7 @@
       <c r="AW392" s="1"/>
       <c r="AX392" s="1"/>
     </row>
-    <row r="393" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -26621,7 +26916,7 @@
       <c r="AW393" s="1"/>
       <c r="AX393" s="1"/>
     </row>
-    <row r="394" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -26673,7 +26968,7 @@
       <c r="AW394" s="1"/>
       <c r="AX394" s="1"/>
     </row>
-    <row r="395" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -26725,7 +27020,7 @@
       <c r="AW395" s="1"/>
       <c r="AX395" s="1"/>
     </row>
-    <row r="396" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -26777,7 +27072,7 @@
       <c r="AW396" s="1"/>
       <c r="AX396" s="1"/>
     </row>
-    <row r="397" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -26829,7 +27124,7 @@
       <c r="AW397" s="1"/>
       <c r="AX397" s="1"/>
     </row>
-    <row r="398" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -26881,7 +27176,7 @@
       <c r="AW398" s="1"/>
       <c r="AX398" s="1"/>
     </row>
-    <row r="399" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -26933,7 +27228,7 @@
       <c r="AW399" s="1"/>
       <c r="AX399" s="1"/>
     </row>
-    <row r="400" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -26985,7 +27280,7 @@
       <c r="AW400" s="1"/>
       <c r="AX400" s="1"/>
     </row>
-    <row r="401" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -27037,7 +27332,7 @@
       <c r="AW401" s="1"/>
       <c r="AX401" s="1"/>
     </row>
-    <row r="402" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -27089,7 +27384,7 @@
       <c r="AW402" s="1"/>
       <c r="AX402" s="1"/>
     </row>
-    <row r="403" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -27141,7 +27436,7 @@
       <c r="AW403" s="1"/>
       <c r="AX403" s="1"/>
     </row>
-    <row r="404" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -27193,7 +27488,7 @@
       <c r="AW404" s="1"/>
       <c r="AX404" s="1"/>
     </row>
-    <row r="405" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -27245,7 +27540,7 @@
       <c r="AW405" s="1"/>
       <c r="AX405" s="1"/>
     </row>
-    <row r="406" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -27297,7 +27592,7 @@
       <c r="AW406" s="1"/>
       <c r="AX406" s="1"/>
     </row>
-    <row r="407" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -27349,7 +27644,7 @@
       <c r="AW407" s="1"/>
       <c r="AX407" s="1"/>
     </row>
-    <row r="408" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -27401,7 +27696,7 @@
       <c r="AW408" s="1"/>
       <c r="AX408" s="1"/>
     </row>
-    <row r="409" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -27453,7 +27748,7 @@
       <c r="AW409" s="1"/>
       <c r="AX409" s="1"/>
     </row>
-    <row r="410" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -27505,7 +27800,7 @@
       <c r="AW410" s="1"/>
       <c r="AX410" s="1"/>
     </row>
-    <row r="411" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -27557,7 +27852,7 @@
       <c r="AW411" s="1"/>
       <c r="AX411" s="1"/>
     </row>
-    <row r="412" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -27609,7 +27904,7 @@
       <c r="AW412" s="1"/>
       <c r="AX412" s="1"/>
     </row>
-    <row r="413" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -27661,7 +27956,7 @@
       <c r="AW413" s="1"/>
       <c r="AX413" s="1"/>
     </row>
-    <row r="414" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -27713,7 +28008,7 @@
       <c r="AW414" s="1"/>
       <c r="AX414" s="1"/>
     </row>
-    <row r="415" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -27765,7 +28060,7 @@
       <c r="AW415" s="1"/>
       <c r="AX415" s="1"/>
     </row>
-    <row r="416" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -27817,7 +28112,7 @@
       <c r="AW416" s="1"/>
       <c r="AX416" s="1"/>
     </row>
-    <row r="417" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -27869,7 +28164,7 @@
       <c r="AW417" s="1"/>
       <c r="AX417" s="1"/>
     </row>
-    <row r="418" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -27921,7 +28216,7 @@
       <c r="AW418" s="1"/>
       <c r="AX418" s="1"/>
     </row>
-    <row r="419" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -27973,7 +28268,7 @@
       <c r="AW419" s="1"/>
       <c r="AX419" s="1"/>
     </row>
-    <row r="420" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -28025,7 +28320,7 @@
       <c r="AW420" s="1"/>
       <c r="AX420" s="1"/>
     </row>
-    <row r="421" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -28077,7 +28372,7 @@
       <c r="AW421" s="1"/>
       <c r="AX421" s="1"/>
     </row>
-    <row r="422" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -28129,7 +28424,7 @@
       <c r="AW422" s="1"/>
       <c r="AX422" s="1"/>
     </row>
-    <row r="423" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -28181,7 +28476,7 @@
       <c r="AW423" s="1"/>
       <c r="AX423" s="1"/>
     </row>
-    <row r="424" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -28233,7 +28528,7 @@
       <c r="AW424" s="1"/>
       <c r="AX424" s="1"/>
     </row>
-    <row r="425" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -28285,7 +28580,7 @@
       <c r="AW425" s="1"/>
       <c r="AX425" s="1"/>
     </row>
-    <row r="426" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -28337,7 +28632,7 @@
       <c r="AW426" s="1"/>
       <c r="AX426" s="1"/>
     </row>
-    <row r="427" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -28389,7 +28684,7 @@
       <c r="AW427" s="1"/>
       <c r="AX427" s="1"/>
     </row>
-    <row r="428" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -28441,7 +28736,7 @@
       <c r="AW428" s="1"/>
       <c r="AX428" s="1"/>
     </row>
-    <row r="429" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -28493,7 +28788,7 @@
       <c r="AW429" s="1"/>
       <c r="AX429" s="1"/>
     </row>
-    <row r="430" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -28545,7 +28840,7 @@
       <c r="AW430" s="1"/>
       <c r="AX430" s="1"/>
     </row>
-    <row r="431" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -28597,7 +28892,7 @@
       <c r="AW431" s="1"/>
       <c r="AX431" s="1"/>
     </row>
-    <row r="432" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -28649,7 +28944,7 @@
       <c r="AW432" s="1"/>
       <c r="AX432" s="1"/>
     </row>
-    <row r="433" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -28701,7 +28996,7 @@
       <c r="AW433" s="1"/>
       <c r="AX433" s="1"/>
     </row>
-    <row r="434" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -28753,7 +29048,7 @@
       <c r="AW434" s="1"/>
       <c r="AX434" s="1"/>
     </row>
-    <row r="435" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -28805,7 +29100,7 @@
       <c r="AW435" s="1"/>
       <c r="AX435" s="1"/>
     </row>
-    <row r="436" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -28857,7 +29152,7 @@
       <c r="AW436" s="1"/>
       <c r="AX436" s="1"/>
     </row>
-    <row r="437" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -28909,7 +29204,7 @@
       <c r="AW437" s="1"/>
       <c r="AX437" s="1"/>
     </row>
-    <row r="438" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -28961,7 +29256,7 @@
       <c r="AW438" s="1"/>
       <c r="AX438" s="1"/>
     </row>
-    <row r="439" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -29013,7 +29308,7 @@
       <c r="AW439" s="1"/>
       <c r="AX439" s="1"/>
     </row>
-    <row r="440" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -29065,7 +29360,7 @@
       <c r="AW440" s="1"/>
       <c r="AX440" s="1"/>
     </row>
-    <row r="441" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -29117,7 +29412,7 @@
       <c r="AW441" s="1"/>
       <c r="AX441" s="1"/>
     </row>
-    <row r="442" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -29169,7 +29464,7 @@
       <c r="AW442" s="1"/>
       <c r="AX442" s="1"/>
     </row>
-    <row r="443" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -29221,7 +29516,7 @@
       <c r="AW443" s="1"/>
       <c r="AX443" s="1"/>
     </row>
-    <row r="444" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -29273,7 +29568,7 @@
       <c r="AW444" s="1"/>
       <c r="AX444" s="1"/>
     </row>
-    <row r="445" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -29325,7 +29620,7 @@
       <c r="AW445" s="1"/>
       <c r="AX445" s="1"/>
     </row>
-    <row r="446" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -29377,7 +29672,7 @@
       <c r="AW446" s="1"/>
       <c r="AX446" s="1"/>
     </row>
-    <row r="447" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -29429,7 +29724,7 @@
       <c r="AW447" s="1"/>
       <c r="AX447" s="1"/>
     </row>
-    <row r="448" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -29481,7 +29776,7 @@
       <c r="AW448" s="1"/>
       <c r="AX448" s="1"/>
     </row>
-    <row r="449" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -29533,7 +29828,7 @@
       <c r="AW449" s="1"/>
       <c r="AX449" s="1"/>
     </row>
-    <row r="450" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -29585,7 +29880,7 @@
       <c r="AW450" s="1"/>
       <c r="AX450" s="1"/>
     </row>
-    <row r="451" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -29637,7 +29932,7 @@
       <c r="AW451" s="1"/>
       <c r="AX451" s="1"/>
     </row>
-    <row r="452" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -29689,7 +29984,7 @@
       <c r="AW452" s="1"/>
       <c r="AX452" s="1"/>
     </row>
-    <row r="453" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -29741,7 +30036,7 @@
       <c r="AW453" s="1"/>
       <c r="AX453" s="1"/>
     </row>
-    <row r="454" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -29793,7 +30088,7 @@
       <c r="AW454" s="1"/>
       <c r="AX454" s="1"/>
     </row>
-    <row r="455" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -29845,7 +30140,7 @@
       <c r="AW455" s="1"/>
       <c r="AX455" s="1"/>
     </row>
-    <row r="456" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -29897,7 +30192,7 @@
       <c r="AW456" s="1"/>
       <c r="AX456" s="1"/>
     </row>
-    <row r="457" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -29949,7 +30244,7 @@
       <c r="AW457" s="1"/>
       <c r="AX457" s="1"/>
     </row>
-    <row r="458" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -30001,7 +30296,7 @@
       <c r="AW458" s="1"/>
       <c r="AX458" s="1"/>
     </row>
-    <row r="459" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -30053,7 +30348,7 @@
       <c r="AW459" s="1"/>
       <c r="AX459" s="1"/>
     </row>
-    <row r="460" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -30105,7 +30400,7 @@
       <c r="AW460" s="1"/>
       <c r="AX460" s="1"/>
     </row>
-    <row r="461" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -30157,7 +30452,7 @@
       <c r="AW461" s="1"/>
       <c r="AX461" s="1"/>
     </row>
-    <row r="462" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -30209,7 +30504,7 @@
       <c r="AW462" s="1"/>
       <c r="AX462" s="1"/>
     </row>
-    <row r="463" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -30261,7 +30556,7 @@
       <c r="AW463" s="1"/>
       <c r="AX463" s="1"/>
     </row>
-    <row r="464" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -30313,7 +30608,7 @@
       <c r="AW464" s="1"/>
       <c r="AX464" s="1"/>
     </row>
-    <row r="465" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -30365,7 +30660,7 @@
       <c r="AW465" s="1"/>
       <c r="AX465" s="1"/>
     </row>
-    <row r="466" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -30417,7 +30712,7 @@
       <c r="AW466" s="1"/>
       <c r="AX466" s="1"/>
     </row>
-    <row r="467" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -30469,7 +30764,7 @@
       <c r="AW467" s="1"/>
       <c r="AX467" s="1"/>
     </row>
-    <row r="468" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -30521,7 +30816,7 @@
       <c r="AW468" s="1"/>
       <c r="AX468" s="1"/>
     </row>
-    <row r="469" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -30573,7 +30868,7 @@
       <c r="AW469" s="1"/>
       <c r="AX469" s="1"/>
     </row>
-    <row r="470" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -30625,7 +30920,7 @@
       <c r="AW470" s="1"/>
       <c r="AX470" s="1"/>
     </row>
-    <row r="471" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -30677,7 +30972,7 @@
       <c r="AW471" s="1"/>
       <c r="AX471" s="1"/>
     </row>
-    <row r="472" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -30729,7 +31024,7 @@
       <c r="AW472" s="1"/>
       <c r="AX472" s="1"/>
     </row>
-    <row r="473" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -30781,7 +31076,7 @@
       <c r="AW473" s="1"/>
       <c r="AX473" s="1"/>
     </row>
-    <row r="474" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -30833,7 +31128,7 @@
       <c r="AW474" s="1"/>
       <c r="AX474" s="1"/>
     </row>
-    <row r="475" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -30885,7 +31180,7 @@
       <c r="AW475" s="1"/>
       <c r="AX475" s="1"/>
     </row>
-    <row r="476" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -30937,7 +31232,7 @@
       <c r="AW476" s="1"/>
       <c r="AX476" s="1"/>
     </row>
-    <row r="477" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -30989,7 +31284,7 @@
       <c r="AW477" s="1"/>
       <c r="AX477" s="1"/>
     </row>
-    <row r="478" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -31041,7 +31336,7 @@
       <c r="AW478" s="1"/>
       <c r="AX478" s="1"/>
     </row>
-    <row r="479" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -31093,7 +31388,7 @@
       <c r="AW479" s="1"/>
       <c r="AX479" s="1"/>
     </row>
-    <row r="480" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -31145,7 +31440,7 @@
       <c r="AW480" s="1"/>
       <c r="AX480" s="1"/>
     </row>
-    <row r="481" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -31197,7 +31492,7 @@
       <c r="AW481" s="1"/>
       <c r="AX481" s="1"/>
     </row>
-    <row r="482" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -31249,7 +31544,7 @@
       <c r="AW482" s="1"/>
       <c r="AX482" s="1"/>
     </row>
-    <row r="483" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -31301,7 +31596,7 @@
       <c r="AW483" s="1"/>
       <c r="AX483" s="1"/>
     </row>
-    <row r="484" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -31353,7 +31648,7 @@
       <c r="AW484" s="1"/>
       <c r="AX484" s="1"/>
     </row>
-    <row r="485" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -31405,7 +31700,7 @@
       <c r="AW485" s="1"/>
       <c r="AX485" s="1"/>
     </row>
-    <row r="486" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -31457,7 +31752,7 @@
       <c r="AW486" s="1"/>
       <c r="AX486" s="1"/>
     </row>
-    <row r="487" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -31509,7 +31804,7 @@
       <c r="AW487" s="1"/>
       <c r="AX487" s="1"/>
     </row>
-    <row r="488" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -31561,7 +31856,7 @@
       <c r="AW488" s="1"/>
       <c r="AX488" s="1"/>
     </row>
-    <row r="489" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -31613,7 +31908,7 @@
       <c r="AW489" s="1"/>
       <c r="AX489" s="1"/>
     </row>
-    <row r="490" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -31665,7 +31960,7 @@
       <c r="AW490" s="1"/>
       <c r="AX490" s="1"/>
     </row>
-    <row r="491" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -31717,7 +32012,7 @@
       <c r="AW491" s="1"/>
       <c r="AX491" s="1"/>
     </row>
-    <row r="492" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -31769,7 +32064,7 @@
       <c r="AW492" s="1"/>
       <c r="AX492" s="1"/>
     </row>
-    <row r="493" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -31821,7 +32116,7 @@
       <c r="AW493" s="1"/>
       <c r="AX493" s="1"/>
     </row>
-    <row r="494" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -31873,7 +32168,7 @@
       <c r="AW494" s="1"/>
       <c r="AX494" s="1"/>
     </row>
-    <row r="495" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -31925,7 +32220,7 @@
       <c r="AW495" s="1"/>
       <c r="AX495" s="1"/>
     </row>
-    <row r="496" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -31977,7 +32272,7 @@
       <c r="AW496" s="1"/>
       <c r="AX496" s="1"/>
     </row>
-    <row r="497" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
